--- a/Mazandasht_v03/02_Bank.xlsx
+++ b/Mazandasht_v03/02_Bank.xlsx
@@ -23,10 +23,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Txn!$A$11:$T$152</definedName>
     <definedName name="AcctTbl">Sync!$H$10:$L$259</definedName>
     <definedName name="BankAccts">Sync!$D$10:$D$19</definedName>
-    <definedName name="BankOpTbl">Sync!$N$10:$S$25</definedName>
+    <definedName name="BankOpTbl">Sync!$N$10:$S$27</definedName>
     <definedName name="BankTbl">Sync!$A$10:$F$19</definedName>
     <definedName name="ListAllCodes">Sync!$H$10:$H$259</definedName>
-    <definedName name="ListBankOps">Sync!$N$10:$N$25</definedName>
+    <definedName name="ListBankOps">Sync!$N$10:$N$27</definedName>
     <definedName name="ListBanks">Sync!$A$10:$A$19</definedName>
     <definedName name="ListChequeStatus">Sync!$U$10:$U$13</definedName>
     <definedName name="ListChequeTypes">Sync!$X$10:$X$11</definedName>
@@ -37,7 +37,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">Card!$A$1:$G$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">Chq!$A$1:$L$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">Flow!$A$1:$H$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">Help!$A$1:$I$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">Help!$A$1:$I$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Home!$A$1:$I$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Post!$A$1:$N$293</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Sum!$A$1:$H$27</definedName>
@@ -328,7 +328,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="769">
   <si>
     <t xml:space="preserve">   مازندشت  ·  سورتینگ و بسته‌بندی مرکبات    ·    MAZANDASHT · CITRUS SORTING &amp; PACKING</t>
   </si>
@@ -539,403 +539,337 @@
 Note</t>
   </si>
   <si>
-    <t>1405/07/01</t>
-  </si>
-  <si>
-    <t>TB-001</t>
+    <t>1405/07/03</t>
+  </si>
+  <si>
+    <t>JB-BS-006</t>
   </si>
   <si>
     <t>واریز پز باسکول (۲۰۰۶)</t>
   </si>
   <si>
-    <t>BANK02</t>
+    <t>BN02</t>
   </si>
   <si>
     <t>کارت/پوز</t>
   </si>
   <si>
-    <t>واریز سرجمع پز ۱۴۰۵/۰۶/۳۱</t>
-  </si>
-  <si>
-    <t>TB-002</t>
+    <t>پوز باسکول — فروش بار (بارفروش)</t>
+  </si>
+  <si>
+    <t>1405/07/04</t>
+  </si>
+  <si>
+    <t>JB-BS-008</t>
+  </si>
+  <si>
+    <t>1405/07/05</t>
+  </si>
+  <si>
+    <t>JB-BS-010</t>
+  </si>
+  <si>
+    <t>تسویه پرداخت (واسط)</t>
+  </si>
+  <si>
+    <t>انتقال بانکی</t>
+  </si>
+  <si>
+    <t>انعام از پوز باسکول</t>
+  </si>
+  <si>
+    <t>1405/07/06</t>
+  </si>
+  <si>
+    <t>JB-RV-001</t>
+  </si>
+  <si>
+    <t>تسویه دریافت (واسط)</t>
+  </si>
+  <si>
+    <t>BN01</t>
+  </si>
+  <si>
+    <t>تسویه بار</t>
+  </si>
+  <si>
+    <t>1405/07/08</t>
+  </si>
+  <si>
+    <t>JB-PV-003</t>
+  </si>
+  <si>
+    <t>پرداخت از واسط</t>
+  </si>
+  <si>
+    <t>1405/07/09</t>
+  </si>
+  <si>
+    <t>JB-RV-002</t>
+  </si>
+  <si>
+    <t>واریز از واسط</t>
+  </si>
+  <si>
+    <t>JB-BS-015</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>JB-PV-004</t>
+  </si>
+  <si>
+    <t>پاس شدن چک</t>
+  </si>
+  <si>
+    <t>1405/07/11</t>
+  </si>
+  <si>
+    <t>JB-RV-003</t>
+  </si>
+  <si>
+    <t>JB-BS-017</t>
+  </si>
+  <si>
+    <t>پوز باسکول — درآمد پوز باسکول (بدون طرف)</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>JB-RV-004</t>
+  </si>
+  <si>
+    <t>1405/07/13</t>
+  </si>
+  <si>
+    <t>TB-901</t>
+  </si>
+  <si>
+    <t>انتقال داخلی بین بانک‌ها</t>
+  </si>
+  <si>
+    <t>BN03</t>
+  </si>
+  <si>
+    <t>انتقال به حساب ملت</t>
+  </si>
+  <si>
+    <t>TR-9001</t>
+  </si>
+  <si>
+    <t>جمع کل</t>
+  </si>
+  <si>
+    <t>تاریخ</t>
+  </si>
+  <si>
+    <t>سند</t>
+  </si>
+  <si>
+    <t>منبع</t>
+  </si>
+  <si>
+    <t>کد حساب</t>
+  </si>
+  <si>
+    <t>نام حساب</t>
+  </si>
+  <si>
+    <t>گروه</t>
+  </si>
+  <si>
+    <t>عملیات</t>
+  </si>
+  <si>
+    <t>بانک</t>
+  </si>
+  <si>
+    <t>بدهکار</t>
+  </si>
+  <si>
+    <t>بستانکار</t>
+  </si>
+  <si>
+    <t>ماه</t>
+  </si>
+  <si>
+    <t>شرح</t>
+  </si>
+  <si>
+    <t>بانک؟</t>
+  </si>
+  <si>
+    <t>مانده و گردش حساب‌های بانکی</t>
+  </si>
+  <si>
+    <t>مانده هر بانک = مانده اولیه + دریافت‌ها − پرداخت‌ها  ·  همه از دفتر تراکنش‌ها</t>
+  </si>
+  <si>
+    <t>جمع مانده بانک‌ها</t>
+  </si>
+  <si>
+    <t>خالص جریان</t>
+  </si>
+  <si>
+    <t>وضعیت هر بانک    به ترتیب مانده</t>
+  </si>
+  <si>
+    <t>مانده اولیه</t>
+  </si>
+  <si>
+    <t>مانده فعلی</t>
+  </si>
+  <si>
+    <t>سهم</t>
+  </si>
+  <si>
+    <t>شماره حساب</t>
+  </si>
+  <si>
+    <t>یادداشت</t>
+  </si>
+  <si>
+    <t>جمع</t>
+  </si>
+  <si>
+    <t>جریان نقدی — ماه به ماه</t>
+  </si>
+  <si>
+    <t>دریافت، پرداخت و خالص هر ماه شمسی  ·  ستون ماه از تاریخ تراکنش ساخته می‌شود</t>
+  </si>
+  <si>
+    <t>بهترین ماه (خالص)</t>
+  </si>
+  <si>
+    <t>بیشترین دریافت</t>
+  </si>
+  <si>
+    <t>بیشترین پرداخت</t>
+  </si>
+  <si>
+    <t>میانگین ماهانه</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>تعداد</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Inflow</t>
+  </si>
+  <si>
+    <t>Outflow</t>
+  </si>
+  <si>
+    <t>خالص</t>
+  </si>
+  <si>
+    <t>Net</t>
+  </si>
+  <si>
+    <t>تجمعی</t>
+  </si>
+  <si>
+    <t>Cumulative</t>
+  </si>
+  <si>
+    <t>نمودار</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>جمع سال</t>
+  </si>
+  <si>
+    <t>تحلیل تراکنش‌ها</t>
+  </si>
+  <si>
+    <t>بر پایه نوع عملیات، روش پرداخت و طرف حساب  ·  سه مدل تحلیل در یک صفحه</t>
+  </si>
+  <si>
+    <t>تحلیل بر اساس نوع عملیات    کدام عملیات بیشترین گردش را دارد؟</t>
+  </si>
+  <si>
+    <t>نوع عملیات</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>سهم پرداخت</t>
+  </si>
+  <si>
+    <t>Share</t>
   </si>
   <si>
     <t>دریافت از مشتری</t>
   </si>
   <si>
-    <t>BANK01</t>
-  </si>
-  <si>
-    <t>انتقال بانکی</t>
-  </si>
-  <si>
-    <t>C001</t>
-  </si>
-  <si>
-    <t>علی‌الحساب خرید مرکبات</t>
-  </si>
-  <si>
-    <t>TR-8841</t>
-  </si>
-  <si>
-    <t>1405/07/02</t>
-  </si>
-  <si>
-    <t>TB-003</t>
+    <t>پرداخت به مشتری</t>
+  </si>
+  <si>
+    <t>دریافت نقدی و واریز به بانک</t>
+  </si>
+  <si>
+    <t>پرداخت هزینه</t>
   </si>
   <si>
     <t>پرداخت انعام مصطفی</t>
   </si>
   <si>
-    <t>انعام هفته اول</t>
-  </si>
-  <si>
-    <t>TB-004</t>
-  </si>
-  <si>
-    <t>انتقال داخلی بین بانک‌ها</t>
-  </si>
-  <si>
-    <t>BANK03</t>
-  </si>
-  <si>
-    <t>تقویت حساب ملت</t>
-  </si>
-  <si>
-    <t>TR-8842</t>
-  </si>
-  <si>
-    <t>1405/07/03</t>
-  </si>
-  <si>
-    <t>TB-005</t>
-  </si>
-  <si>
-    <t>پرداخت به مشتری</t>
+    <t>دریافت هزینه باسکول دیگران</t>
+  </si>
+  <si>
+    <t>پرداخت به باسکول دیگران</t>
+  </si>
+  <si>
+    <t>پاس چک (پرداخت چک)</t>
+  </si>
+  <si>
+    <t>برگشت چک دریافتی</t>
+  </si>
+  <si>
+    <t>واریز چک به حساب</t>
+  </si>
+  <si>
+    <t>دریافت تسهیلات</t>
+  </si>
+  <si>
+    <t>بازپرداخت تسهیلات</t>
+  </si>
+  <si>
+    <t>سایر دریافت</t>
+  </si>
+  <si>
+    <t>سایر پرداخت</t>
+  </si>
+  <si>
+    <t>تحلیل بر اساس روش پرداخت    نقد، چک، انتقال، کارت/پوز، حواله</t>
+  </si>
+  <si>
+    <t>روش</t>
+  </si>
+  <si>
+    <t>نقد</t>
+  </si>
+  <si>
+    <t>چک</t>
   </si>
   <si>
     <t>حواله</t>
-  </si>
-  <si>
-    <t>C002</t>
-  </si>
-  <si>
-    <t>تسویه بخشی از حساب باغدار</t>
-  </si>
-  <si>
-    <t>TR-8843</t>
-  </si>
-  <si>
-    <t>TB-006</t>
-  </si>
-  <si>
-    <t>دریافت هزینه باسکول دیگران</t>
-  </si>
-  <si>
-    <t>هزینه باسکول میدان بار</t>
-  </si>
-  <si>
-    <t>BD001 – باسکول میدان بار (نمونه)</t>
-  </si>
-  <si>
-    <t>1405/07/04</t>
-  </si>
-  <si>
-    <t>TB-007</t>
-  </si>
-  <si>
-    <t>واریز پز ۱۴۰۵/۰۷/۰۳</t>
-  </si>
-  <si>
-    <t>1405/07/05</t>
-  </si>
-  <si>
-    <t>TB-008</t>
-  </si>
-  <si>
-    <t>پرداخت هزینه</t>
-  </si>
-  <si>
-    <t>X012</t>
-  </si>
-  <si>
-    <t>هزینه حمل و تخلیه</t>
-  </si>
-  <si>
-    <t>1405/07/06</t>
-  </si>
-  <si>
-    <t>TB-009</t>
-  </si>
-  <si>
-    <t>پاس چک (پرداخت چک)</t>
-  </si>
-  <si>
-    <t>پاس چک</t>
-  </si>
-  <si>
-    <t>چک ۴۵۲۱ به تأمین‌کننده</t>
-  </si>
-  <si>
-    <t>4521</t>
-  </si>
-  <si>
-    <t>1405/07/07</t>
-  </si>
-  <si>
-    <t>TB-010</t>
-  </si>
-  <si>
-    <t>C003</t>
-  </si>
-  <si>
-    <t>واریز بابت فاکتور بار</t>
-  </si>
-  <si>
-    <t>TR-8844</t>
-  </si>
-  <si>
-    <t>1405/07/08</t>
-  </si>
-  <si>
-    <t>TB-011</t>
-  </si>
-  <si>
-    <t>دریافت نقدی و واریز به بانک</t>
-  </si>
-  <si>
-    <t>نقد</t>
-  </si>
-  <si>
-    <t>واریز نقدی صندوق</t>
-  </si>
-  <si>
-    <t>1405/07/09</t>
-  </si>
-  <si>
-    <t>TB-012</t>
-  </si>
-  <si>
-    <t>S001</t>
-  </si>
-  <si>
-    <t>پرداخت به فروشنده سبد</t>
-  </si>
-  <si>
-    <t>1405/07/10</t>
-  </si>
-  <si>
-    <t>TB-013</t>
-  </si>
-  <si>
-    <t>واریز پز ۱۴۰۵/۰۷/۰۹</t>
-  </si>
-  <si>
-    <t>1405/07/11</t>
-  </si>
-  <si>
-    <t>TB-014</t>
-  </si>
-  <si>
-    <t>پرداخت به باسکول دیگران</t>
-  </si>
-  <si>
-    <t>تسویه با باسکول میدان بار</t>
-  </si>
-  <si>
-    <t>1405/07/12</t>
-  </si>
-  <si>
-    <t>TB-015</t>
-  </si>
-  <si>
-    <t>سایر دریافت</t>
-  </si>
-  <si>
-    <t>C005</t>
-  </si>
-  <si>
-    <t>دریافت متفرقه</t>
-  </si>
-  <si>
-    <t>جمع کل</t>
-  </si>
-  <si>
-    <t>تاریخ</t>
-  </si>
-  <si>
-    <t>سند</t>
-  </si>
-  <si>
-    <t>منبع</t>
-  </si>
-  <si>
-    <t>کد حساب</t>
-  </si>
-  <si>
-    <t>نام حساب</t>
-  </si>
-  <si>
-    <t>گروه</t>
-  </si>
-  <si>
-    <t>عملیات</t>
-  </si>
-  <si>
-    <t>بانک</t>
-  </si>
-  <si>
-    <t>بدهکار</t>
-  </si>
-  <si>
-    <t>بستانکار</t>
-  </si>
-  <si>
-    <t>ماه</t>
-  </si>
-  <si>
-    <t>شرح</t>
-  </si>
-  <si>
-    <t>بانک؟</t>
-  </si>
-  <si>
-    <t>مانده و گردش حساب‌های بانکی</t>
-  </si>
-  <si>
-    <t>مانده هر بانک = مانده اولیه + دریافت‌ها − پرداخت‌ها  ·  همه از دفتر تراکنش‌ها</t>
-  </si>
-  <si>
-    <t>جمع مانده بانک‌ها</t>
-  </si>
-  <si>
-    <t>خالص جریان</t>
-  </si>
-  <si>
-    <t>وضعیت هر بانک    به ترتیب مانده</t>
-  </si>
-  <si>
-    <t>مانده اولیه</t>
-  </si>
-  <si>
-    <t>مانده فعلی</t>
-  </si>
-  <si>
-    <t>سهم</t>
-  </si>
-  <si>
-    <t>شماره حساب</t>
-  </si>
-  <si>
-    <t>یادداشت</t>
-  </si>
-  <si>
-    <t>جمع</t>
-  </si>
-  <si>
-    <t>جریان نقدی — ماه به ماه</t>
-  </si>
-  <si>
-    <t>دریافت، پرداخت و خالص هر ماه شمسی  ·  ستون ماه از تاریخ تراکنش ساخته می‌شود</t>
-  </si>
-  <si>
-    <t>بهترین ماه (خالص)</t>
-  </si>
-  <si>
-    <t>بیشترین دریافت</t>
-  </si>
-  <si>
-    <t>بیشترین پرداخت</t>
-  </si>
-  <si>
-    <t>میانگین ماهانه</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>تعداد</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Inflow</t>
-  </si>
-  <si>
-    <t>Outflow</t>
-  </si>
-  <si>
-    <t>خالص</t>
-  </si>
-  <si>
-    <t>Net</t>
-  </si>
-  <si>
-    <t>تجمعی</t>
-  </si>
-  <si>
-    <t>Cumulative</t>
-  </si>
-  <si>
-    <t>نمودار</t>
-  </si>
-  <si>
-    <t>Bar</t>
-  </si>
-  <si>
-    <t>جمع سال</t>
-  </si>
-  <si>
-    <t>تحلیل تراکنش‌ها</t>
-  </si>
-  <si>
-    <t>بر پایه نوع عملیات، روش پرداخت و طرف حساب  ·  سه مدل تحلیل در یک صفحه</t>
-  </si>
-  <si>
-    <t>تحلیل بر اساس نوع عملیات    کدام عملیات بیشترین گردش را دارد؟</t>
-  </si>
-  <si>
-    <t>نوع عملیات</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>In</t>
-  </si>
-  <si>
-    <t>Out</t>
-  </si>
-  <si>
-    <t>سهم پرداخت</t>
-  </si>
-  <si>
-    <t>Share</t>
-  </si>
-  <si>
-    <t>برگشت چک دریافتی</t>
-  </si>
-  <si>
-    <t>واریز چک به حساب</t>
-  </si>
-  <si>
-    <t>دریافت تسهیلات</t>
-  </si>
-  <si>
-    <t>بازپرداخت تسهیلات</t>
-  </si>
-  <si>
-    <t>سایر پرداخت</t>
-  </si>
-  <si>
-    <t>تحلیل بر اساس روش پرداخت    نقد، چک، انتقال، کارت/پوز، حواله</t>
-  </si>
-  <si>
-    <t>روش</t>
-  </si>
-  <si>
-    <t>چک</t>
   </si>
   <si>
     <t>بزرگ‌ترین طرف حساب‌ها    جمع گردش هر طرف حساب در دفتر تراکنش‌ها</t>
@@ -1055,12 +989,21 @@
 Cleared</t>
   </si>
   <si>
+    <t>1405/07/02</t>
+  </si>
+  <si>
     <t>1405/08/02</t>
   </si>
   <si>
+    <t>4521</t>
+  </si>
+  <si>
     <t>پرداختی</t>
   </si>
   <si>
+    <t>X012</t>
+  </si>
+  <si>
     <t>حمل و تخلیه</t>
   </si>
   <si>
@@ -1073,6 +1016,9 @@
     <t>دریافتی</t>
   </si>
   <si>
+    <t>C002</t>
+  </si>
+  <si>
     <t>چک باغدار</t>
   </si>
   <si>
@@ -1136,9 +1082,6 @@
     <t>صادرات ۹۰۰۹ — جاری اصلی</t>
   </si>
   <si>
-    <t>BN01</t>
-  </si>
-  <si>
     <t>بله</t>
   </si>
   <si>
@@ -1148,87 +1091,63 @@
     <t>صادرات ۲۰۰۶ — پوز باسکول</t>
   </si>
   <si>
-    <t>BN02</t>
-  </si>
-  <si>
     <t>پوز باسکول به این حساب وصل است</t>
   </si>
   <si>
     <t>ملت</t>
   </si>
   <si>
-    <t>BN03</t>
-  </si>
-  <si>
-    <t>BANK04</t>
+    <t>BN04</t>
   </si>
   <si>
     <t>کشاورزی</t>
   </si>
   <si>
-    <t>BN04</t>
-  </si>
-  <si>
-    <t>BANK05</t>
+    <t>BN05</t>
   </si>
   <si>
     <t>سپه</t>
   </si>
   <si>
-    <t>BN05</t>
-  </si>
-  <si>
-    <t>BANK06</t>
+    <t>BN06</t>
   </si>
   <si>
     <t>مهر ایران</t>
   </si>
   <si>
-    <t>BN06</t>
-  </si>
-  <si>
-    <t>BANK07</t>
+    <t>BN07</t>
   </si>
   <si>
     <t>تجارت</t>
   </si>
   <si>
-    <t>BN07</t>
-  </si>
-  <si>
-    <t>BANK08</t>
+    <t>BN08</t>
   </si>
   <si>
     <t>پاسارگاد</t>
   </si>
   <si>
-    <t>BN08</t>
-  </si>
-  <si>
-    <t>BANK09</t>
+    <t>BN09</t>
   </si>
   <si>
     <t>رفاه</t>
   </si>
   <si>
-    <t>BN09</t>
-  </si>
-  <si>
-    <t>BANK10</t>
+    <t>BN10</t>
   </si>
   <si>
     <t>قرض‌الحسنه</t>
   </si>
   <si>
-    <t>BN10</t>
-  </si>
-  <si>
     <t>حساب‌ها (همه طرف‌حساب‌ها و حساب‌های معین)</t>
   </si>
   <si>
     <t>ACCOUNTS</t>
   </si>
   <si>
+    <t>C001</t>
+  </si>
+  <si>
     <t>زینب زاهدی</t>
   </si>
   <si>
@@ -1247,6 +1166,9 @@
     <t>صادراتی</t>
   </si>
   <si>
+    <t>C003</t>
+  </si>
+  <si>
     <t>حاج احمد عیسی پور</t>
   </si>
   <si>
@@ -1256,6 +1178,9 @@
     <t>امید زاهدی</t>
   </si>
   <si>
+    <t>C005</t>
+  </si>
+  <si>
     <t>بار شخصی قاسم زاهدی</t>
   </si>
   <si>
@@ -1604,6 +1529,9 @@
     <t>زنجان — خانی</t>
   </si>
   <si>
+    <t>S001</t>
+  </si>
+  <si>
     <t>حسن کوچک‌زاده</t>
   </si>
   <si>
@@ -1772,12 +1700,15 @@
     <t>X011</t>
   </si>
   <si>
-    <t>حساب واسط عملیات</t>
+    <t>حساب واسط بانک و پز (در راه)</t>
   </si>
   <si>
     <t>حساب واسط</t>
   </si>
   <si>
+    <t>هزینه حمل و تخلیه</t>
+  </si>
+  <si>
     <t>هزینه دستمزد</t>
   </si>
   <si>
@@ -2426,7 +2357,7 @@
     <t>B09</t>
   </si>
   <si>
-    <t>واریزی سرجمع پز روز قبل به حساب ۲۰۰۶</t>
+    <t>سرجمع پز روز قبل؛ حساب واسط X011 را تسویه می‌کند (درآمد در دفتر روزنامه ثبت شده)</t>
   </si>
   <si>
     <t>B10</t>
@@ -2465,6 +2396,18 @@
     <t>B16</t>
   </si>
   <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>واریزی‌ای که قبلاً در شیت پرداخت (Pay) ثبت شده؛ واسط X011 را صفر می‌کند</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>پرداختی که قبلاً در شیت پرداخت (Pay) ثبت شده؛ واسط X011 را صفر می‌کند</t>
+  </si>
+  <si>
     <t>روش پرداخت</t>
   </si>
   <si>
@@ -2483,6 +2426,9 @@
     <t>OTHER SCALES</t>
   </si>
   <si>
+    <t>BD001 – باسکول میدان بار (نمونه)</t>
+  </si>
+  <si>
     <t>BD002 – (بدون نام)</t>
   </si>
   <si>
@@ -2573,6 +2519,12 @@
     <t xml:space="preserve">     •  هر تراکنش دو خط دفتر می‌سازد: خط بانک و خط طرف حساب.</t>
   </si>
   <si>
+    <t xml:space="preserve">     •  کد حساب‌های بانکی در همه فایل‌ها BNxx است (BN01…BN10). در دفتر روزنامه (01_Entry) هیچ سندی مستقیم روی BNxx زده نمی‌شود: هر حرکت بانکی از حساب واسط X011 عبور می‌کند و مانده واقعی هر بانک فقط از همین فایل (شیت Post) خوانده می‌شود.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     •  دفتر روزنامه تنها دفتر مالی است: هر رویداد اقتصادی (فروش، هزینه، بدهی) باید در 01_Entry ثبت شود و این فایل حرکت واقعی پول را. برای هزینه‌ای که از بانک پرداخت می‌شود، در 01_Entry یک «پرداخت» با روش «انتقال بانکی» و حساب هزینه بزنید و همین‌جا همان مبلغ را با نوع «تسویه پرداخت (واسط)» ثبت کنید.</t>
+  </si>
+  <si>
     <t xml:space="preserve">کشوها از کجا می‌آیند؟    </t>
   </si>
   <si>
@@ -2582,7 +2534,7 @@
     <t xml:space="preserve">     •  بانک عامل و بانک مقصد ← شیت Bnk فایل مادر.</t>
   </si>
   <si>
-    <t xml:space="preserve">     •  نوع عملیات بانکی ← جدول «Bank Operations» در شیت List فایل مادر (۱۶ نوع، قابل افزودن).</t>
+    <t xml:space="preserve">     •  نوع عملیات بانکی ← جدول «Bank Operations» در شیت List فایل مادر (۱۸ نوع، قابل افزودن).</t>
   </si>
   <si>
     <t xml:space="preserve">     •  روش پرداخت و وضعیت چک ← شیت List.</t>
@@ -2612,6 +2564,9 @@
     <t xml:space="preserve">     •  نتیجه: خط اول بستانکار بانک مبدأ، خط دوم بدهکار بانک مقصد؛ جمع شرکت صفر می‌ماند.</t>
   </si>
   <si>
+    <t xml:space="preserve">     •  دفتر روزنامه برای «انتقال داخلی» هیچ سندی نمی‌سازد، چون پولی از شرکت خارج نمی‌شود؛ فقط همین فایل هر دو طرف را ثبت می‌کند. در شیت پرداخت 01_Entry هم روش «انتقال داخلی» را انتخاب کنید تا سند اضافه زده نشود.</t>
+  </si>
+  <si>
     <t xml:space="preserve">انعام مصطفی    </t>
   </si>
   <si>
@@ -2624,7 +2579,7 @@
     <t xml:space="preserve">     •  برای دیدن مانده انعام مصطفی، در شیت Post ستون کد حساب را روی X001 فیلتر کنید.</t>
   </si>
   <si>
-    <t xml:space="preserve">     •  کنترل خودکار ۲۰۰۶ ↔ مصطفی در شیت POS فایل 01_Entry انجام می‌شود و باید صفر بماند.</t>
+    <t xml:space="preserve">     •  کنترل خودکار ۲۰۰۶ ↔ مصطفی در شیت POS فایل 01_Entry (کنترل مانده واسط X011) انجام می‌شود و باید صفر بماند.</t>
   </si>
   <si>
     <t xml:space="preserve">باسکول دیگران    </t>
@@ -2672,7 +2627,10 @@
     <t xml:space="preserve">     •  در انتهای Txn جمع بدهکار و بستانکار باید برابر باشند؛ کادر «تراز» سبز می‌شود.</t>
   </si>
   <si>
-    <t xml:space="preserve">     •  شیت Card: جمع پز باسکول این فایل با جمع پز شیت POS در 01_Entry مقایسه می‌شود.</t>
+    <t xml:space="preserve">     •  شیت Card: واریزی پز باسکول هر بانک با پز ثبت‌شده در دفتر روزنامه مقایسه می‌شود؛ این دو باید برابر باشند.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     •  اگر نوع عملیات را از گروه «تسویه…» انتخاب نکنید (مثلاً «پرداخت هزینه» با کد طرف حساب)، آن مبلغ در دفتر روزنامه سند ندارد و جمع واسط X011 صفر نمی‌شود؛ شیت 05_Bal (شیت Audit) این اختلاف را نشان می‌دهد.</t>
   </si>
   <si>
     <t xml:space="preserve">چاپ و صفحه‌آرایی    </t>
@@ -2702,7 +2660,10 @@
     <t xml:space="preserve">     •  08_Dash ← داشبوردی که هم از این فایل و هم از 01_Entry می‌خواند.</t>
   </si>
   <si>
-    <t xml:space="preserve">     •  03_Report / 04_Inv / 05_Bal ← گزارش‌ها و صورت‌حساب‌ها.</t>
+    <t xml:space="preserve">     •  05_Bal ← مانده هر بانک در شیت IBank از همین فایل (Post) خوانده می‌شود؛ جمع آن با شیت SUM همین فایل و داشبورد یکی است.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     •  03_Report / 04_Inv ← گزارش‌ها و صورت‌حساب‌ها.</t>
   </si>
 </sst>
 </file>
@@ -7322,7 +7283,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9" ht="6" customHeight="1">
@@ -7351,7 +7312,7 @@
     </row>
     <row r="3" spans="1:9" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -7364,7 +7325,7 @@
     </row>
     <row r="4" spans="1:9" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -7388,7 +7349,7 @@
     </row>
     <row r="7" spans="1:9" ht="26.25" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -7403,7 +7364,7 @@
     </row>
     <row r="8" spans="1:9" ht="32.25" customHeight="1">
       <c r="A8" s="88" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="B8" s="88"/>
       <c r="C8" s="88"/>
@@ -7416,7 +7377,7 @@
     </row>
     <row r="9" spans="1:9" ht="27.75" customHeight="1">
       <c r="A9" s="89" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="B9" s="89"/>
       <c r="C9" s="89"/>
@@ -7429,7 +7390,7 @@
     </row>
     <row r="10" spans="1:9" ht="27.75" customHeight="1">
       <c r="A10" s="89" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="B10" s="89"/>
       <c r="C10" s="89"/>
@@ -7440,63 +7401,63 @@
       <c r="H10" s="89"/>
       <c r="I10" s="89"/>
     </row>
-    <row r="12" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12" t="s">
+    <row r="11" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A11" s="89" t="s">
+        <v>720</v>
+      </c>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="89"/>
+    </row>
+    <row r="12" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A12" s="89" t="s">
+        <v>721</v>
+      </c>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
+    </row>
+    <row r="14" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A13" s="88" t="s">
-        <v>739</v>
-      </c>
-      <c r="B13" s="88"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-    </row>
-    <row r="14" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A14" s="89" t="s">
-        <v>740</v>
-      </c>
-      <c r="B14" s="89"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-    </row>
-    <row r="15" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A15" s="89" t="s">
-        <v>741</v>
-      </c>
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A15" s="88" t="s">
+        <v>723</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
     </row>
     <row r="16" spans="1:9" ht="27.75" customHeight="1">
       <c r="A16" s="89" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="B16" s="89"/>
       <c r="C16" s="89"/>
@@ -7509,7 +7470,7 @@
     </row>
     <row r="17" spans="1:9" ht="27.75" customHeight="1">
       <c r="A17" s="89" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="B17" s="89"/>
       <c r="C17" s="89"/>
@@ -7522,7 +7483,7 @@
     </row>
     <row r="18" spans="1:9" ht="27.75" customHeight="1">
       <c r="A18" s="89" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="B18" s="89"/>
       <c r="C18" s="89"/>
@@ -7533,63 +7494,63 @@
       <c r="H18" s="89"/>
       <c r="I18" s="89"/>
     </row>
-    <row r="20" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A20" s="11" t="s">
-        <v>745</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A21" s="88" t="s">
-        <v>746</v>
-      </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="88"/>
-    </row>
-    <row r="22" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A22" s="89" t="s">
-        <v>747</v>
-      </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-    </row>
-    <row r="23" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A23" s="89" t="s">
-        <v>748</v>
-      </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
+    <row r="19" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A19" s="89" t="s">
+        <v>727</v>
+      </c>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+    </row>
+    <row r="20" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A20" s="89" t="s">
+        <v>728</v>
+      </c>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+    </row>
+    <row r="22" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A22" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A23" s="88" t="s">
+        <v>730</v>
+      </c>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
     </row>
     <row r="24" spans="1:9" ht="27.75" customHeight="1">
       <c r="A24" s="89" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="B24" s="89"/>
       <c r="C24" s="89"/>
@@ -7602,7 +7563,7 @@
     </row>
     <row r="25" spans="1:9" ht="27.75" customHeight="1">
       <c r="A25" s="89" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B25" s="89"/>
       <c r="C25" s="89"/>
@@ -7613,199 +7574,210 @@
       <c r="H25" s="89"/>
       <c r="I25" s="89"/>
     </row>
-    <row r="27" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A27" s="11" t="s">
-        <v>751</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12" t="s">
-        <v>752</v>
-      </c>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A28" s="88" t="s">
-        <v>753</v>
-      </c>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-    </row>
-    <row r="29" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A29" s="89" t="s">
-        <v>754</v>
-      </c>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-    </row>
-    <row r="30" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A30" s="89" t="s">
-        <v>755</v>
-      </c>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-    </row>
-    <row r="32" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>756</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12" t="s">
-        <v>757</v>
-      </c>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A33" s="88" t="s">
-        <v>758</v>
-      </c>
-      <c r="B33" s="88"/>
-      <c r="C33" s="88"/>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-    </row>
-    <row r="34" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A34" s="89" t="s">
-        <v>759</v>
-      </c>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-    </row>
-    <row r="35" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A35" s="89" t="s">
-        <v>760</v>
-      </c>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-    </row>
-    <row r="36" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A36" s="89" t="s">
-        <v>761</v>
-      </c>
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
-    </row>
-    <row r="38" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A38" s="11" t="s">
-        <v>762</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>763</v>
-      </c>
-      <c r="I38" s="12"/>
-    </row>
-    <row r="39" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A39" s="88" t="s">
-        <v>764</v>
-      </c>
-      <c r="B39" s="88"/>
-      <c r="C39" s="88"/>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="88"/>
-      <c r="H39" s="88"/>
-      <c r="I39" s="88"/>
-    </row>
-    <row r="40" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A40" s="89" t="s">
-        <v>765</v>
-      </c>
-      <c r="B40" s="89"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-    </row>
-    <row r="41" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A41" s="89" t="s">
-        <v>766</v>
-      </c>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-    </row>
-    <row r="43" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A43" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12" t="s">
-        <v>768</v>
-      </c>
-      <c r="I43" s="12"/>
+    <row r="26" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A26" s="89" t="s">
+        <v>733</v>
+      </c>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="89"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="89"/>
+    </row>
+    <row r="27" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A27" s="89" t="s">
+        <v>734</v>
+      </c>
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+    </row>
+    <row r="28" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A28" s="89" t="s">
+        <v>735</v>
+      </c>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+    </row>
+    <row r="30" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A30" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="12" t="s">
+        <v>737</v>
+      </c>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A31" s="88" t="s">
+        <v>738</v>
+      </c>
+      <c r="B31" s="88"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+    </row>
+    <row r="32" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A32" s="89" t="s">
+        <v>739</v>
+      </c>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="89"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="89"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="89"/>
+    </row>
+    <row r="33" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A33" s="89" t="s">
+        <v>740</v>
+      </c>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
+    </row>
+    <row r="35" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A35" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="36" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A36" s="88" t="s">
+        <v>743</v>
+      </c>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+    </row>
+    <row r="37" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A37" s="89" t="s">
+        <v>744</v>
+      </c>
+      <c r="B37" s="89"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="89"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="89"/>
+    </row>
+    <row r="38" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A38" s="89" t="s">
+        <v>745</v>
+      </c>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="89"/>
+    </row>
+    <row r="39" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A39" s="89" t="s">
+        <v>746</v>
+      </c>
+      <c r="B39" s="89"/>
+      <c r="C39" s="89"/>
+      <c r="D39" s="89"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="89"/>
+    </row>
+    <row r="41" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A41" s="11" t="s">
+        <v>747</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="12" t="s">
+        <v>748</v>
+      </c>
+      <c r="I41" s="12"/>
+    </row>
+    <row r="42" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A42" s="88" t="s">
+        <v>749</v>
+      </c>
+      <c r="B42" s="88"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="88"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="88"/>
+    </row>
+    <row r="43" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A43" s="89" t="s">
+        <v>750</v>
+      </c>
+      <c r="B43" s="89"/>
+      <c r="C43" s="89"/>
+      <c r="D43" s="89"/>
+      <c r="E43" s="89"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="89"/>
     </row>
     <row r="44" spans="1:9" ht="27.75" customHeight="1">
       <c r="A44" s="89" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="B44" s="89"/>
       <c r="C44" s="89"/>
@@ -7816,63 +7788,63 @@
       <c r="H44" s="89"/>
       <c r="I44" s="89"/>
     </row>
-    <row r="45" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A45" s="89" t="s">
-        <v>770</v>
-      </c>
-      <c r="B45" s="89"/>
-      <c r="C45" s="89"/>
-      <c r="D45" s="89"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="89"/>
-      <c r="G45" s="89"/>
-      <c r="H45" s="89"/>
-      <c r="I45" s="89"/>
-    </row>
-    <row r="46" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A46" s="89" t="s">
-        <v>771</v>
-      </c>
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="89"/>
-      <c r="I46" s="89"/>
-    </row>
-    <row r="48" spans="1:9" ht="26.25" customHeight="1">
-      <c r="A48" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A49" s="88" t="s">
-        <v>774</v>
-      </c>
-      <c r="B49" s="88"/>
-      <c r="C49" s="88"/>
-      <c r="D49" s="88"/>
-      <c r="E49" s="88"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="88"/>
-      <c r="I49" s="88"/>
+    <row r="46" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A46" s="11" t="s">
+        <v>752</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="I46" s="12"/>
+    </row>
+    <row r="47" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A47" s="89" t="s">
+        <v>754</v>
+      </c>
+      <c r="B47" s="89"/>
+      <c r="C47" s="89"/>
+      <c r="D47" s="89"/>
+      <c r="E47" s="89"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89"/>
+    </row>
+    <row r="48" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A48" s="89" t="s">
+        <v>755</v>
+      </c>
+      <c r="B48" s="89"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="89"/>
+      <c r="E48" s="89"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="89"/>
+    </row>
+    <row r="49" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A49" s="89" t="s">
+        <v>756</v>
+      </c>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
     </row>
     <row r="50" spans="1:9" ht="27.75" customHeight="1">
       <c r="A50" s="89" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="B50" s="89"/>
       <c r="C50" s="89"/>
@@ -7885,7 +7857,7 @@
     </row>
     <row r="52" spans="1:9" ht="26.25" customHeight="1">
       <c r="A52" s="11" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
@@ -7894,26 +7866,26 @@
       <c r="F52" s="11"/>
       <c r="G52" s="11"/>
       <c r="H52" s="12" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A53" s="89" t="s">
-        <v>778</v>
-      </c>
-      <c r="B53" s="89"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="89"/>
+    <row r="53" spans="1:9" ht="32.25" customHeight="1">
+      <c r="A53" s="88" t="s">
+        <v>760</v>
+      </c>
+      <c r="B53" s="88"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
     </row>
     <row r="54" spans="1:9" ht="27.75" customHeight="1">
       <c r="A54" s="89" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="B54" s="89"/>
       <c r="C54" s="89"/>
@@ -7924,34 +7896,88 @@
       <c r="H54" s="89"/>
       <c r="I54" s="89"/>
     </row>
-    <row r="55" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A55" s="89" t="s">
-        <v>780</v>
-      </c>
-      <c r="B55" s="89"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
-    </row>
-    <row r="56" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A56" s="89" t="s">
-        <v>781</v>
-      </c>
-      <c r="B56" s="89"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="89"/>
+    <row r="56" spans="1:9" ht="26.25" customHeight="1">
+      <c r="A56" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="I56" s="12"/>
+    </row>
+    <row r="57" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A57" s="89" t="s">
+        <v>764</v>
+      </c>
+      <c r="B57" s="89"/>
+      <c r="C57" s="89"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="89"/>
+      <c r="F57" s="89"/>
+      <c r="G57" s="89"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="89"/>
+    </row>
+    <row r="58" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A58" s="89" t="s">
+        <v>765</v>
+      </c>
+      <c r="B58" s="89"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="89"/>
+      <c r="E58" s="89"/>
+      <c r="F58" s="89"/>
+      <c r="G58" s="89"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="89"/>
+    </row>
+    <row r="59" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A59" s="89" t="s">
+        <v>766</v>
+      </c>
+      <c r="B59" s="89"/>
+      <c r="C59" s="89"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
+      <c r="H59" s="89"/>
+      <c r="I59" s="89"/>
+    </row>
+    <row r="60" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A60" s="89" t="s">
+        <v>767</v>
+      </c>
+      <c r="B60" s="89"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+    </row>
+    <row r="61" spans="1:9" ht="27.75" customHeight="1">
+      <c r="A61" s="89" t="s">
+        <v>768</v>
+      </c>
+      <c r="B61" s="89"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="89"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="59">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
@@ -7960,52 +7986,57 @@
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="H14:I14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:I22"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="H35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A48:I48"/>
     <mergeCell ref="A49:I49"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="H52:I52"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A54:I54"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A61:I61"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.28" right="0.28" top="0.42" bottom="0.48" header="0.22" footer="0.22"/>
@@ -8379,9 +8410,11 @@
       <c r="K13" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="L13" s="28"/>
+      <c r="L13" s="28" t="s">
+        <v>64</v>
+      </c>
       <c r="M13" s="31">
-        <v>120000000</v>
+        <v>120000</v>
       </c>
       <c r="N13" s="29"/>
       <c r="O13" s="32">
@@ -8436,24 +8469,22 @@
         <v>0</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F14" s="29"/>
       <c r="G14" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>73</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H14" s="28"/>
       <c r="I14" s="30">
         <f>IF($H14="","",IFERROR(VLOOKUP($H14,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -8463,13 +8494,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="29" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M14" s="31">
-        <v>150000000</v>
+        <v>90000</v>
       </c>
       <c r="N14" s="29"/>
       <c r="O14" s="32">
@@ -8524,20 +8555,20 @@
         <v>0</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>66</v>
       </c>
       <c r="F15" s="29"/>
       <c r="G15" s="28" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H15" s="28"/>
       <c r="I15" s="30">
@@ -8549,11 +8580,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" s="28"/>
+        <v>75</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>72</v>
+      </c>
       <c r="M15" s="31">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="N15" s="29"/>
       <c r="O15" s="32">
@@ -8611,19 +8644,17 @@
         <v>76</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>82</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F16" s="29"/>
       <c r="G16" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="28"/>
       <c r="I16" s="30">
@@ -8635,13 +8666,13 @@
         <v>0</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="M16" s="31">
-        <v>200000000</v>
+        <v>300000000</v>
       </c>
       <c r="N16" s="29"/>
       <c r="O16" s="32">
@@ -8696,24 +8727,22 @@
         <v>0</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F17" s="29"/>
       <c r="G17" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>89</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="H17" s="28"/>
       <c r="I17" s="30">
         <f>IF($H17="","",IFERROR(VLOOKUP($H17,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -8723,13 +8752,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="M17" s="31">
-        <v>60000000</v>
+        <v>80000000</v>
       </c>
       <c r="N17" s="29"/>
       <c r="O17" s="32">
@@ -8784,20 +8813,20 @@
         <v>0</v>
       </c>
       <c r="B18" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>92</v>
-      </c>
       <c r="D18" s="29" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>66</v>
       </c>
       <c r="F18" s="29"/>
       <c r="G18" s="28" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H18" s="28"/>
       <c r="I18" s="30">
@@ -8809,15 +8838,15 @@
         <v>0</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="L18" s="28"/>
+        <v>86</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>85</v>
+      </c>
       <c r="M18" s="31">
-        <v>1500000</v>
-      </c>
-      <c r="N18" s="29" t="s">
-        <v>95</v>
-      </c>
+        <v>120000000</v>
+      </c>
+      <c r="N18" s="29"/>
       <c r="O18" s="32">
         <f>IF($B18="",0,IF($U18="IN",N($M18),0))</f>
         <v>0</v>
@@ -8870,10 +8899,10 @@
         <v>0</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D19" s="29" t="s">
         <v>65</v>
@@ -8895,11 +8924,13 @@
         <v>0</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="L19" s="28"/>
+        <v>68</v>
+      </c>
+      <c r="L19" s="28" t="s">
+        <v>87</v>
+      </c>
       <c r="M19" s="31">
-        <v>95000000</v>
+        <v>80000</v>
       </c>
       <c r="N19" s="29"/>
       <c r="O19" s="32">
@@ -8954,24 +8985,22 @@
         <v>0</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F20" s="29"/>
       <c r="G20" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>102</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="H20" s="28"/>
       <c r="I20" s="30">
         <f>IF($H20="","",IFERROR(VLOOKUP($H20,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -8981,11 +9010,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="L20" s="28"/>
+        <v>90</v>
+      </c>
+      <c r="L20" s="28" t="s">
+        <v>89</v>
+      </c>
       <c r="M20" s="31">
-        <v>12000000</v>
+        <v>200000000</v>
       </c>
       <c r="N20" s="29"/>
       <c r="O20" s="32">
@@ -9040,20 +9071,20 @@
         <v>0</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F21" s="29"/>
       <c r="G21" s="28" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="H21" s="28"/>
       <c r="I21" s="30">
@@ -9065,13 +9096,13 @@
         <v>0</v>
       </c>
       <c r="K21" s="29" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="L21" s="28" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="M21" s="31">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="N21" s="29"/>
       <c r="O21" s="32">
@@ -9126,24 +9157,22 @@
         <v>0</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F22" s="29"/>
       <c r="G22" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>112</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H22" s="28"/>
       <c r="I22" s="30">
         <f>IF($H22="","",IFERROR(VLOOKUP($H22,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -9153,13 +9182,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="29" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L22" s="28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="M22" s="31">
-        <v>88000000</v>
+        <v>300000</v>
       </c>
       <c r="N22" s="29"/>
       <c r="O22" s="32">
@@ -9214,20 +9243,20 @@
         <v>0</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F23" s="29"/>
       <c r="G23" s="28" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="H23" s="28"/>
       <c r="I23" s="30">
@@ -9239,11 +9268,13 @@
         <v>0</v>
       </c>
       <c r="K23" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="L23" s="28"/>
+        <v>86</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>96</v>
+      </c>
       <c r="M23" s="31">
-        <v>25000000</v>
+        <v>50000000</v>
       </c>
       <c r="N23" s="29"/>
       <c r="O23" s="32">
@@ -9298,24 +9329,24 @@
         <v>0</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="29"/>
+        <v>79</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>100</v>
+      </c>
       <c r="G24" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>122</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="H24" s="28"/>
       <c r="I24" s="30">
         <f>IF($H24="","",IFERROR(VLOOKUP($H24,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -9325,11 +9356,13 @@
         <v>0</v>
       </c>
       <c r="K24" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="L24" s="28"/>
+        <v>101</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>102</v>
+      </c>
       <c r="M24" s="31">
-        <v>33000000</v>
+        <v>50000000</v>
       </c>
       <c r="N24" s="29"/>
       <c r="O24" s="32">
@@ -9383,22 +9416,12 @@
         <f>IF($B25="","",COUNTA($B$13:$B25))</f>
         <v>0</v>
       </c>
-      <c r="B25" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>66</v>
-      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="28" t="s">
-        <v>67</v>
-      </c>
+      <c r="G25" s="28"/>
       <c r="H25" s="28"/>
       <c r="I25" s="30">
         <f>IF($H25="","",IFERROR(VLOOKUP($H25,AcctTbl,2,0),"کد ناشناخته"))</f>
@@ -9408,13 +9431,9 @@
         <f>IF($H25="","",IFERROR(VLOOKUP($H25,AcctTbl,3,0),""))</f>
         <v>0</v>
       </c>
-      <c r="K25" s="29" t="s">
-        <v>126</v>
-      </c>
+      <c r="K25" s="29"/>
       <c r="L25" s="28"/>
-      <c r="M25" s="31">
-        <v>76000000</v>
-      </c>
+      <c r="M25" s="31"/>
       <c r="N25" s="29"/>
       <c r="O25" s="32">
         <f>IF($B25="",0,IF($U25="IN",N($M25),0))</f>
@@ -9467,22 +9486,12 @@
         <f>IF($B26="","",COUNTA($B$13:$B26))</f>
         <v>0</v>
       </c>
-      <c r="B26" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>66</v>
-      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="29"/>
-      <c r="G26" s="28" t="s">
-        <v>67</v>
-      </c>
+      <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="I26" s="30">
         <f>IF($H26="","",IFERROR(VLOOKUP($H26,AcctTbl,2,0),"کد ناشناخته"))</f>
@@ -9492,16 +9501,10 @@
         <f>IF($H26="","",IFERROR(VLOOKUP($H26,AcctTbl,3,0),""))</f>
         <v>0</v>
       </c>
-      <c r="K26" s="29" t="s">
-        <v>130</v>
-      </c>
+      <c r="K26" s="29"/>
       <c r="L26" s="28"/>
-      <c r="M26" s="31">
-        <v>1000000</v>
-      </c>
-      <c r="N26" s="29" t="s">
-        <v>95</v>
-      </c>
+      <c r="M26" s="31"/>
+      <c r="N26" s="29"/>
       <c r="O26" s="32">
         <f>IF($B26="",0,IF($U26="IN",N($M26),0))</f>
         <v>0</v>
@@ -9553,25 +9556,13 @@
         <f>IF($B27="","",COUNTA($B$13:$B27))</f>
         <v>0</v>
       </c>
-      <c r="B27" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>82</v>
-      </c>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="29"/>
-      <c r="G27" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>134</v>
-      </c>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="30">
         <f>IF($H27="","",IFERROR(VLOOKUP($H27,AcctTbl,2,0),"کد ناشناخته"))</f>
         <v>0</v>
@@ -9580,13 +9571,9 @@
         <f>IF($H27="","",IFERROR(VLOOKUP($H27,AcctTbl,3,0),""))</f>
         <v>0</v>
       </c>
-      <c r="K27" s="29" t="s">
-        <v>135</v>
-      </c>
+      <c r="K27" s="29"/>
       <c r="L27" s="28"/>
-      <c r="M27" s="31">
-        <v>9500000</v>
-      </c>
+      <c r="M27" s="31"/>
       <c r="N27" s="29"/>
       <c r="O27" s="32">
         <f>IF($B27="",0,IF($U27="IN",N($M27),0))</f>
@@ -18386,7 +18373,7 @@
     </row>
     <row r="153" spans="1:26" ht="24" customHeight="1">
       <c r="A153" s="34" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="B153" s="34"/>
       <c r="C153" s="34"/>
@@ -18519,44 +18506,44 @@
   <sheetData>
     <row r="9" spans="1:14">
       <c r="A9" s="37" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="I9" s="37" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="K9" s="37" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L9" s="37" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="M9" s="37"/>
       <c r="N9" s="37" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -33729,7 +33716,7 @@
     </row>
     <row r="3" spans="1:8" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -33741,7 +33728,7 @@
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -33763,7 +33750,7 @@
     </row>
     <row r="7" spans="1:8" ht="20.25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
@@ -33775,7 +33762,7 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -33803,7 +33790,7 @@
     </row>
     <row r="10" spans="1:8" ht="26.25" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -33817,10 +33804,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="43" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>4</v>
@@ -33829,16 +33816,16 @@
         <v>5</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="H11" s="43" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21.75" customHeight="1">
@@ -34183,7 +34170,7 @@
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="50" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="B22" s="51">
         <f>SUM(B12:B21)</f>
@@ -34270,7 +34257,7 @@
     </row>
     <row r="3" spans="1:8" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -34282,7 +34269,7 @@
     </row>
     <row r="4" spans="1:8" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -34304,19 +34291,19 @@
     </row>
     <row r="7" spans="1:8" ht="20.25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -34344,10 +34331,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="54" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C11" s="54" t="s">
         <v>4</v>
@@ -34356,36 +34343,36 @@
         <v>5</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="55" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -34738,7 +34725,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="50" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="B25" s="51">
         <f>SUM(B13:B24)</f>
@@ -34819,7 +34806,7 @@
     </row>
     <row r="3" spans="1:7" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -34830,7 +34817,7 @@
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -34850,7 +34837,7 @@
     </row>
     <row r="7" spans="1:7" ht="26.25" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -34863,10 +34850,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="54" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C8" s="54" t="s">
         <v>4</v>
@@ -34875,41 +34862,41 @@
         <v>5</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="55" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="F9" s="55" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G9" s="55" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="62" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="B10" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A10)</f>
@@ -34938,7 +34925,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="62" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="B11" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A11)</f>
@@ -34967,7 +34954,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="62" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="B12" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A12)</f>
@@ -34996,7 +34983,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="62" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="B13" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A13)</f>
@@ -35025,7 +35012,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="62" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B14" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A14)</f>
@@ -35054,7 +35041,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="62" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="B15" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A15)</f>
@@ -35083,7 +35070,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="62" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="B16" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A16)</f>
@@ -35112,7 +35099,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="62" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="B17" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A17)</f>
@@ -35170,7 +35157,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="62" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="B19" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A19)</f>
@@ -35199,7 +35186,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="62" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B20" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A20)</f>
@@ -35228,7 +35215,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="62" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B21" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A21)</f>
@@ -35257,7 +35244,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="62" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B22" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A22)</f>
@@ -35286,7 +35273,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="62" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="B23" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A23)</f>
@@ -35315,7 +35302,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="62" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="B24" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A24)</f>
@@ -35344,7 +35331,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="62" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B25" s="45">
         <f>COUNTIF(Txn!$D$13:$D$152,$A25)</f>
@@ -35371,9 +35358,67 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="45">
+        <f>COUNTIF(Txn!$D$13:$D$152,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="57">
+        <f>SUMIFS(Txn!$M$13:$M$152,Txn!$D$13:$D$152,$A26,Txn!$U$13:$U$152,"IN")</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="58">
+        <f>SUMIFS(Txn!$M$13:$M$152,Txn!$D$13:$D$152,$A26,Txn!$U$13:$U$152,"OUT")</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="59">
+        <f>$C26-$D26</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="63">
+        <f>IFERROR($D26/SUM($D$10:$D$25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="64">
+        <f>REPT("█",MIN(16,ROUND(MAX($C26,$D26)/MAX(1,MAX($C$10:$C$25),MAX($D$10:$D$25))*16,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="45">
+        <f>COUNTIF(Txn!$D$13:$D$152,$A27)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="57">
+        <f>SUMIFS(Txn!$M$13:$M$152,Txn!$D$13:$D$152,$A27,Txn!$U$13:$U$152,"IN")</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="58">
+        <f>SUMIFS(Txn!$M$13:$M$152,Txn!$D$13:$D$152,$A27,Txn!$U$13:$U$152,"OUT")</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="59">
+        <f>$C27-$D27</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="63">
+        <f>IFERROR($D27/SUM($D$10:$D$25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="64">
+        <f>REPT("█",MIN(16,ROUND(MAX($C27,$D27)/MAX(1,MAX($C$10:$C$25),MAX($D$10:$D$25))*16,0)))</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="28" spans="1:7" ht="26.25" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -35386,10 +35431,10 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="65" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B29" s="65" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C29" s="65" t="s">
         <v>4</v>
@@ -35398,15 +35443,15 @@
         <v>5</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="F29" s="65" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="62" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="B30" s="45">
         <f>COUNTIFS(Txn!$G$13:$G$152,$A30)</f>
@@ -35431,7 +35476,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="62" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B31" s="45">
         <f>COUNTIFS(Txn!$G$13:$G$152,$A31)</f>
@@ -35456,7 +35501,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="62" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B32" s="45">
         <f>COUNTIFS(Txn!$G$13:$G$152,$A32)</f>
@@ -35506,7 +35551,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="62" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="B34" s="45">
         <f>COUNTIFS(Txn!$G$13:$G$152,$A34)</f>
@@ -35531,35 +35576,35 @@
     </row>
     <row r="37" spans="1:7" ht="26.25" customHeight="1">
       <c r="A37" s="11" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="12" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="66" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D38" s="66" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="E38" s="66" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F38" s="66" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -35772,7 +35817,7 @@
     </row>
     <row r="48" spans="1:7" ht="33.75" customHeight="1">
       <c r="A48" s="70" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="B48" s="70"/>
       <c r="C48" s="70"/>
@@ -35842,7 +35887,7 @@
     </row>
     <row r="3" spans="1:7" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -35853,7 +35898,7 @@
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -35873,19 +35918,19 @@
     </row>
     <row r="7" spans="1:7" ht="20.25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="33.75" customHeight="1">
@@ -35911,48 +35956,48 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="54" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="C11" s="54" t="s">
         <v>67</v>
       </c>
       <c r="D11" s="54" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="55" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="E12" s="55" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -36257,7 +36302,7 @@
     </row>
     <row r="35" spans="1:7" ht="33.75" customHeight="1">
       <c r="A35" s="25" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -36341,7 +36386,7 @@
     </row>
     <row r="3" spans="1:12" ht="38.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -36357,7 +36402,7 @@
     </row>
     <row r="4" spans="1:12" ht="21.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -36387,25 +36432,25 @@
     </row>
     <row r="7" spans="1:12" ht="20.25" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L7" s="6"/>
     </row>
@@ -36443,34 +36488,34 @@
         <v>43</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>61</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="L12" s="26" t="s">
         <v>62</v>
@@ -36482,38 +36527,38 @@
         <v>0</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="G13" s="30">
         <f>IF($F13="","",IFERROR(VLOOKUP($F13,AcctTbl,2,0),""))</f>
         <v>0</v>
       </c>
       <c r="H13" s="77" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I13" s="31">
         <v>40000000</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="K13" s="28" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="L13" s="77" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="21" customHeight="1">
@@ -36522,36 +36567,36 @@
         <v>0</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="G14" s="30">
         <f>IF($F14="","",IFERROR(VLOOKUP($F14,AcctTbl,2,0),""))</f>
         <v>0</v>
       </c>
       <c r="H14" s="77" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I14" s="31">
         <v>65000000</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="K14" s="28"/>
       <c r="L14" s="77" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="21" customHeight="1">
@@ -36560,36 +36605,36 @@
         <v>0</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="G15" s="30">
         <f>IF($F15="","",IFERROR(VLOOKUP($F15,AcctTbl,2,0),""))</f>
         <v>0</v>
       </c>
       <c r="H15" s="77" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I15" s="31">
         <v>18000000</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="K15" s="28"/>
       <c r="L15" s="77" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="21" customHeight="1">
@@ -36598,19 +36643,19 @@
         <v>0</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="G16" s="30">
         <f>IF($F16="","",IFERROR(VLOOKUP($F16,AcctTbl,2,0),""))</f>
@@ -36623,11 +36668,11 @@
         <v>42000000</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="K16" s="28"/>
       <c r="L16" s="77" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="21" customHeight="1">
@@ -36636,36 +36681,36 @@
         <v>0</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="G17" s="30">
         <f>IF($F17="","",IFERROR(VLOOKUP($F17,AcctTbl,2,0),""))</f>
         <v>0</v>
       </c>
       <c r="H17" s="77" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="I17" s="31">
         <v>22000000</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="K17" s="28"/>
       <c r="L17" s="77" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="21" customHeight="1">
@@ -36674,32 +36719,32 @@
         <v>0</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="G18" s="30">
         <f>IF($F18="","",IFERROR(VLOOKUP($F18,AcctTbl,2,0),""))</f>
         <v>0</v>
       </c>
       <c r="H18" s="77" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I18" s="31">
         <v>51000000</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="K18" s="28"/>
       <c r="L18" s="77"/>
@@ -37871,7 +37916,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" s="79" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -37898,7 +37943,7 @@
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1">
       <c r="A2" s="80" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B2" s="80"/>
       <c r="C2" s="80"/>
@@ -37925,7 +37970,7 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="43" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -37933,14 +37978,14 @@
       <c r="E9" s="43"/>
       <c r="F9" s="43"/>
       <c r="H9" s="81" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="I9" s="81"/>
       <c r="J9" s="81"/>
       <c r="K9" s="81"/>
       <c r="L9" s="81"/>
       <c r="N9" s="82" t="s">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="O9" s="82"/>
       <c r="P9" s="82"/>
@@ -37948,85 +37993,85 @@
       <c r="R9" s="82"/>
       <c r="S9" s="82"/>
       <c r="T9" s="83" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="U9" s="83" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="V9" s="83" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="W9" s="83" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="X9" s="83" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="84" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C10" s="86">
         <v>500000000</v>
       </c>
       <c r="D10" s="84" t="s">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="E10" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F10" s="85" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="H10" s="84" t="s">
-        <v>73</v>
+        <v>262</v>
       </c>
       <c r="I10" s="85" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="J10" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K10" s="85" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="L10" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N10" s="85" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="O10" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P10" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q10" s="84"/>
       <c r="R10" s="84" t="s">
-        <v>667</v>
+        <v>644</v>
       </c>
       <c r="S10" s="87" t="s">
-        <v>668</v>
+        <v>645</v>
       </c>
       <c r="T10" s="85" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="U10" s="85" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="V10" s="85" t="s">
-        <v>95</v>
+        <v>689</v>
       </c>
       <c r="W10" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="X10" s="85" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -38034,2200 +38079,2236 @@
         <v>66</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="C11" s="86">
         <v>0</v>
       </c>
       <c r="D11" s="84" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="E11" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F11" s="85" t="s">
+        <v>244</v>
+      </c>
+      <c r="H11" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" s="85" t="s">
+        <v>267</v>
+      </c>
+      <c r="J11" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="H11" s="84" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="85" t="s">
-        <v>294</v>
-      </c>
-      <c r="J11" s="85" t="s">
-        <v>291</v>
-      </c>
       <c r="K11" s="85" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="L11" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N11" s="85" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="O11" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P11" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q11" s="84"/>
       <c r="R11" s="84" t="s">
-        <v>670</v>
+        <v>647</v>
       </c>
       <c r="S11" s="87" t="s">
-        <v>671</v>
+        <v>648</v>
       </c>
       <c r="T11" s="85" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="U11" s="85" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="V11" s="85" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="W11" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="X11" s="85" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="84" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C12" s="86">
         <v>0</v>
       </c>
       <c r="D12" s="84" t="s">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F12" s="85"/>
       <c r="H12" s="84" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="I12" s="85" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="J12" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K12" s="85" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="L12" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N12" s="85" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="O12" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P12" s="84" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="Q12" s="84" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="R12" s="84" t="s">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="S12" s="87" t="s">
-        <v>674</v>
+        <v>651</v>
       </c>
       <c r="T12" s="85" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="U12" s="85" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="V12" s="85" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="W12" s="85" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="84" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="C13" s="86">
         <v>0</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="E13" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F13" s="85"/>
       <c r="H13" s="84" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="I13" s="85" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="J13" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K13" s="85"/>
       <c r="L13" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N13" s="85" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="O13" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P13" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q13" s="84"/>
       <c r="R13" s="84" t="s">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="S13" s="87" t="s">
-        <v>676</v>
+        <v>653</v>
       </c>
       <c r="T13" s="85" t="s">
         <v>67</v>
       </c>
       <c r="U13" s="85" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="V13" s="85" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="W13" s="85" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="84" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C14" s="86">
         <v>0</v>
       </c>
       <c r="D14" s="84" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="E14" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F14" s="85"/>
       <c r="H14" s="84" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="I14" s="85" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="J14" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K14" s="85"/>
       <c r="L14" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N14" s="85" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="O14" s="84" t="s">
-        <v>677</v>
+        <v>654</v>
       </c>
       <c r="P14" s="84" t="s">
-        <v>678</v>
+        <v>655</v>
       </c>
       <c r="Q14" s="84"/>
       <c r="R14" s="84" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="S14" s="87" t="s">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="T14" s="85" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="V14" s="85" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="W14" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="84" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="C15" s="86">
         <v>0</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="E15" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F15" s="85"/>
       <c r="H15" s="84" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="I15" s="85" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="J15" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K15" s="85"/>
       <c r="L15" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N15" s="85" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="O15" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P15" s="84" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="Q15" s="84" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="R15" s="84" t="s">
-        <v>681</v>
+        <v>658</v>
       </c>
       <c r="S15" s="87" t="s">
-        <v>682</v>
+        <v>659</v>
       </c>
       <c r="V15" s="85" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="W15" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="84" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C16" s="86">
         <v>0</v>
       </c>
       <c r="D16" s="84" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="E16" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F16" s="85"/>
       <c r="H16" s="84" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="I16" s="85" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="J16" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K16" s="85"/>
       <c r="L16" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N16" s="85" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="O16" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P16" s="84" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="Q16" s="84"/>
       <c r="R16" s="84" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="S16" s="87" t="s">
-        <v>685</v>
+        <v>662</v>
       </c>
       <c r="V16" s="85" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="W16" s="85" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="84" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="C17" s="86">
         <v>0</v>
       </c>
       <c r="D17" s="84" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="E17" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F17" s="85"/>
       <c r="H17" s="84" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="I17" s="85" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="J17" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K17" s="85"/>
       <c r="L17" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N17" s="85" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="O17" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P17" s="84" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="Q17" s="84"/>
       <c r="R17" s="84" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="S17" s="87" t="s">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="V17" s="85" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="W17" s="85" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="84" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="C18" s="86">
         <v>0</v>
       </c>
       <c r="D18" s="84" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="E18" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F18" s="85"/>
       <c r="H18" s="84" t="s">
-        <v>306</v>
+        <v>281</v>
       </c>
       <c r="I18" s="85" t="s">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="J18" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K18" s="85"/>
       <c r="L18" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N18" s="85" t="s">
         <v>65</v>
       </c>
       <c r="O18" s="84" t="s">
+        <v>642</v>
+      </c>
+      <c r="P18" s="84" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q18" s="84" t="s">
+        <v>446</v>
+      </c>
+      <c r="R18" s="84" t="s">
         <v>665</v>
       </c>
-      <c r="P18" s="84" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q18" s="84" t="s">
-        <v>445</v>
-      </c>
-      <c r="R18" s="84" t="s">
-        <v>688</v>
-      </c>
       <c r="S18" s="87" t="s">
-        <v>689</v>
+        <v>666</v>
       </c>
       <c r="V18" s="85" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="W18" s="85" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="84" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="B19" s="85" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="C19" s="86">
         <v>0</v>
       </c>
       <c r="D19" s="84" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="E19" s="84" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F19" s="85"/>
       <c r="H19" s="84" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="I19" s="85" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="J19" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K19" s="85"/>
       <c r="L19" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N19" s="85" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="O19" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P19" s="84" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="Q19" s="84" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="R19" s="84" t="s">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="S19" s="87" t="s">
-        <v>691</v>
+        <v>668</v>
       </c>
       <c r="V19" s="85" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="W19" s="85" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="H20" s="84" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="I20" s="85" t="s">
-        <v>311</v>
+        <v>286</v>
       </c>
       <c r="J20" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K20" s="85"/>
       <c r="L20" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N20" s="85" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="O20" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P20" s="84" t="s">
-        <v>672</v>
+        <v>649</v>
       </c>
       <c r="Q20" s="84" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="R20" s="84" t="s">
-        <v>692</v>
+        <v>669</v>
       </c>
       <c r="S20" s="87" t="s">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="V20" s="85" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="H21" s="84" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="I21" s="85" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="J21" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K21" s="85"/>
       <c r="L21" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N21" s="85" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="O21" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P21" s="84" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q21" s="84" t="s">
+        <v>443</v>
+      </c>
+      <c r="R21" s="84" t="s">
+        <v>671</v>
+      </c>
+      <c r="S21" s="87" t="s">
         <v>672</v>
       </c>
-      <c r="Q21" s="84" t="s">
-        <v>467</v>
-      </c>
-      <c r="R21" s="84" t="s">
-        <v>694</v>
-      </c>
-      <c r="S21" s="87" t="s">
-        <v>695</v>
-      </c>
       <c r="V21" s="85" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
     </row>
     <row r="22" spans="1:23">
       <c r="H22" s="84" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="I22" s="85" t="s">
-        <v>315</v>
+        <v>290</v>
       </c>
       <c r="J22" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K22" s="85"/>
       <c r="L22" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N22" s="85" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="O22" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P22" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q22" s="84"/>
       <c r="R22" s="84" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="S22" s="87" t="s">
-        <v>697</v>
+        <v>674</v>
       </c>
       <c r="V22" s="85" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
     </row>
     <row r="23" spans="1:23">
       <c r="H23" s="84" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="I23" s="85" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="J23" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K23" s="85"/>
       <c r="L23" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N23" s="85" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="O23" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P23" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q23" s="84"/>
       <c r="R23" s="84" t="s">
-        <v>698</v>
+        <v>675</v>
       </c>
       <c r="S23" s="87" t="s">
-        <v>699</v>
+        <v>676</v>
       </c>
       <c r="V23" s="85" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
     </row>
     <row r="24" spans="1:23">
       <c r="H24" s="84" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="I24" s="85" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="J24" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K24" s="85"/>
       <c r="L24" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N24" s="85" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="O24" s="84" t="s">
-        <v>665</v>
+        <v>642</v>
       </c>
       <c r="P24" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q24" s="84"/>
       <c r="R24" s="84" t="s">
-        <v>700</v>
+        <v>677</v>
       </c>
       <c r="S24" s="87"/>
       <c r="V24" s="85" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
     </row>
     <row r="25" spans="1:23">
       <c r="H25" s="84" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="I25" s="85" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="J25" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K25" s="85"/>
       <c r="L25" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="N25" s="85" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="O25" s="84" t="s">
-        <v>669</v>
+        <v>646</v>
       </c>
       <c r="P25" s="84" t="s">
-        <v>666</v>
+        <v>643</v>
       </c>
       <c r="Q25" s="84"/>
       <c r="R25" s="84" t="s">
-        <v>701</v>
+        <v>678</v>
       </c>
       <c r="S25" s="87"/>
       <c r="V25" s="85" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="H26" s="84" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="I26" s="85" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="J26" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K26" s="85"/>
       <c r="L26" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
+      </c>
+      <c r="N26" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="O26" s="84" t="s">
+        <v>642</v>
+      </c>
+      <c r="P26" s="84" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q26" s="84" t="s">
+        <v>446</v>
+      </c>
+      <c r="R26" s="84" t="s">
+        <v>679</v>
+      </c>
+      <c r="S26" s="87" t="s">
+        <v>680</v>
       </c>
       <c r="V26" s="85" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
     </row>
     <row r="27" spans="1:23">
       <c r="H27" s="84" t="s">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="I27" s="85" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="J27" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K27" s="85"/>
       <c r="L27" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
+      </c>
+      <c r="N27" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="O27" s="84" t="s">
+        <v>646</v>
+      </c>
+      <c r="P27" s="84" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q27" s="84" t="s">
+        <v>446</v>
+      </c>
+      <c r="R27" s="84" t="s">
+        <v>681</v>
+      </c>
+      <c r="S27" s="87" t="s">
+        <v>682</v>
       </c>
       <c r="V27" s="85" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:23">
       <c r="H28" s="84" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="I28" s="85" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="J28" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K28" s="85"/>
       <c r="L28" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="V28" s="85" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
     </row>
     <row r="29" spans="1:23">
       <c r="H29" s="84" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="I29" s="85" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="J29" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K29" s="85"/>
       <c r="L29" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="V29" s="85" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
     </row>
     <row r="30" spans="1:23">
       <c r="H30" s="84" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="I30" s="85" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="J30" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K30" s="85"/>
       <c r="L30" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:23">
       <c r="H31" s="84" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="I31" s="85" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="J31" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K31" s="85"/>
       <c r="L31" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:23">
       <c r="H32" s="84" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="I32" s="85" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="J32" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K32" s="85"/>
       <c r="L32" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="8:12">
       <c r="H33" s="84" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="I33" s="85" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="J33" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K33" s="85"/>
       <c r="L33" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="34" spans="8:12">
       <c r="H34" s="84" t="s">
-        <v>338</v>
+        <v>313</v>
       </c>
       <c r="I34" s="85" t="s">
-        <v>339</v>
+        <v>314</v>
       </c>
       <c r="J34" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K34" s="85"/>
       <c r="L34" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="8:12">
       <c r="H35" s="84" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="I35" s="85" t="s">
-        <v>341</v>
+        <v>316</v>
       </c>
       <c r="J35" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K35" s="85"/>
       <c r="L35" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="8:12">
       <c r="H36" s="84" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="I36" s="85" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="J36" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K36" s="85"/>
       <c r="L36" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="8:12">
       <c r="H37" s="84" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="I37" s="85" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="J37" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K37" s="85"/>
       <c r="L37" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="8:12">
       <c r="H38" s="84" t="s">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="I38" s="85" t="s">
-        <v>347</v>
+        <v>322</v>
       </c>
       <c r="J38" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K38" s="85"/>
       <c r="L38" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="8:12">
       <c r="H39" s="84" t="s">
-        <v>348</v>
+        <v>323</v>
       </c>
       <c r="I39" s="85" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="J39" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K39" s="85"/>
       <c r="L39" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="8:12">
       <c r="H40" s="84" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="I40" s="85" t="s">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="J40" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K40" s="85"/>
       <c r="L40" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="8:12">
       <c r="H41" s="84" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="I41" s="85" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
       <c r="J41" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K41" s="85"/>
       <c r="L41" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="8:12">
       <c r="H42" s="84" t="s">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="I42" s="85" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="J42" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K42" s="85"/>
       <c r="L42" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="8:12">
       <c r="H43" s="84" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="I43" s="85" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="J43" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K43" s="85"/>
       <c r="L43" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="8:12">
       <c r="H44" s="84" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="I44" s="85" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="J44" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K44" s="85"/>
       <c r="L44" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45" spans="8:12">
       <c r="H45" s="84" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="I45" s="85" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="J45" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K45" s="85"/>
       <c r="L45" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" spans="8:12">
       <c r="H46" s="84" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="I46" s="85" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="J46" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K46" s="85"/>
       <c r="L46" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" spans="8:12">
       <c r="H47" s="84" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="I47" s="85" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="J47" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K47" s="85"/>
       <c r="L47" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="8:12">
       <c r="H48" s="84" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="I48" s="85" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="J48" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K48" s="85"/>
       <c r="L48" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="8:12">
       <c r="H49" s="84" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="I49" s="85" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="J49" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K49" s="85"/>
       <c r="L49" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="8:12">
       <c r="H50" s="84" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="I50" s="85" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="J50" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K50" s="85"/>
       <c r="L50" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="8:12">
       <c r="H51" s="84" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="I51" s="85" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="J51" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K51" s="85"/>
       <c r="L51" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52" spans="8:12">
       <c r="H52" s="84" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="I52" s="85" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="J52" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K52" s="85"/>
       <c r="L52" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="8:12">
       <c r="H53" s="84" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="I53" s="85" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="J53" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K53" s="85"/>
       <c r="L53" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54" spans="8:12">
       <c r="H54" s="84" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="I54" s="85" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="J54" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K54" s="85"/>
       <c r="L54" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55" spans="8:12">
       <c r="H55" s="84" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="I55" s="85" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="J55" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K55" s="85"/>
       <c r="L55" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="8:12">
       <c r="H56" s="84" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="I56" s="85" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="J56" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K56" s="85"/>
       <c r="L56" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="8:12">
       <c r="H57" s="84" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="I57" s="85" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="J57" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K57" s="85"/>
       <c r="L57" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" spans="8:12">
       <c r="H58" s="84" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="I58" s="85" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
       <c r="J58" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K58" s="85"/>
       <c r="L58" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="8:12">
       <c r="H59" s="84" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="I59" s="85" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="J59" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K59" s="85"/>
       <c r="L59" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="8:12">
       <c r="H60" s="84" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="I60" s="85" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="J60" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K60" s="85"/>
       <c r="L60" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="8:12">
       <c r="H61" s="84" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
       <c r="I61" s="85" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="J61" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K61" s="85"/>
       <c r="L61" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="8:12">
       <c r="H62" s="84" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="I62" s="85" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="J62" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K62" s="85"/>
       <c r="L62" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="8:12">
       <c r="H63" s="84" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="I63" s="85" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="J63" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K63" s="85"/>
       <c r="L63" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64" spans="8:12">
       <c r="H64" s="84" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="I64" s="85" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="J64" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K64" s="85"/>
       <c r="L64" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="8:12">
       <c r="H65" s="84" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="I65" s="85" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="J65" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K65" s="85"/>
       <c r="L65" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="8:12">
       <c r="H66" s="84" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="I66" s="85" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="J66" s="85" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="K66" s="85"/>
       <c r="L66" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" spans="8:12">
       <c r="H67" s="84" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="I67" s="85" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="J67" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K67" s="85" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="L67" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="8:12">
       <c r="H68" s="84" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="I68" s="85" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="J68" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K68" s="85" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="L68" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="8:12">
       <c r="H69" s="84" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="I69" s="85" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="J69" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K69" s="85" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="L69" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="8:12">
       <c r="H70" s="84" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="I70" s="85" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="J70" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K70" s="85" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="L70" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="8:12">
       <c r="H71" s="84" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="I71" s="85" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="J71" s="85" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K71" s="85" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="L71" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" spans="8:12">
       <c r="H72" s="84" t="s">
-        <v>122</v>
+        <v>390</v>
       </c>
       <c r="I72" s="85" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="J72" s="85" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="K72" s="85" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="L72" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="8:12">
       <c r="H73" s="84" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="I73" s="85" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="J73" s="85" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="K73" s="85" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="L73" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="8:12">
       <c r="H74" s="84" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="I74" s="85" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="J74" s="85" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="K74" s="85" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="L74" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="8:12">
       <c r="H75" s="84" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="I75" s="85" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="J75" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K75" s="85" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="L75" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" spans="8:12">
       <c r="H76" s="84" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="I76" s="85" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="J76" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K76" s="85" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="L76" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="8:12">
       <c r="H77" s="84" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="I77" s="85" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="J77" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K77" s="85" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="L77" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="8:12">
       <c r="H78" s="84" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="I78" s="85" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="J78" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K78" s="85" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="L78" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="8:12">
       <c r="H79" s="84" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="I79" s="85" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="J79" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K79" s="85" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="L79" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="8:12">
       <c r="H80" s="84" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="I80" s="85" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="J80" s="85" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K80" s="85" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="L80" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="8:12">
       <c r="H81" s="84" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="I81" s="85" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="J81" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K81" s="85" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="L81" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="8:12">
       <c r="H82" s="84" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="I82" s="85" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="J82" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K82" s="85" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="L82" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="83" spans="8:12">
       <c r="H83" s="84" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="I83" s="85" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="J83" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K83" s="85" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="L83" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="84" spans="8:12">
       <c r="H84" s="84" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="I84" s="85" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="J84" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K84" s="85" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="L84" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="85" spans="8:12">
       <c r="H85" s="84" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="I85" s="85" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="J85" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K85" s="85" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="L85" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="86" spans="8:12">
       <c r="H86" s="84" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="I86" s="85" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="J86" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K86" s="85" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L86" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="87" spans="8:12">
       <c r="H87" s="84" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="I87" s="85" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="J87" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K87" s="85" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L87" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88" spans="8:12">
       <c r="H88" s="84" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="I88" s="85" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="J88" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K88" s="85" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L88" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="89" spans="8:12">
       <c r="H89" s="84" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="I89" s="85" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="J89" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K89" s="85" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="L89" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90" spans="8:12">
       <c r="H90" s="84" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="I90" s="85" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="J90" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K90" s="85" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="L90" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91" spans="8:12">
       <c r="H91" s="84" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="I91" s="85" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="J91" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K91" s="85" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="L91" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="92" spans="8:12">
       <c r="H92" s="84" t="s">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="I92" s="85" t="s">
-        <v>103</v>
+        <v>449</v>
       </c>
       <c r="J92" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K92" s="85" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="L92" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="93" spans="8:12">
       <c r="H93" s="84" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="I93" s="85" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="J93" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K93" s="85" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="L93" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="8:12">
       <c r="H94" s="84" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="I94" s="85" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="J94" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K94" s="85" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="L94" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="8:12">
       <c r="H95" s="84" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="I95" s="85" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="J95" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K95" s="85" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L95" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="96" spans="8:12">
       <c r="H96" s="84" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="I96" s="85" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="J96" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K96" s="85" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="L96" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="97" spans="8:12">
       <c r="H97" s="84" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="I97" s="85" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
       <c r="J97" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K97" s="85" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="L97" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="98" spans="8:12">
       <c r="H98" s="84" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="I98" s="85" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="J98" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K98" s="85" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L98" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="99" spans="8:12">
       <c r="H99" s="84" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="I99" s="85" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="J99" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K99" s="85" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="L99" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="100" spans="8:12">
       <c r="H100" s="84" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="I100" s="85" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="J100" s="85" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="K100" s="85" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="L100" s="84" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="101" spans="8:12">
       <c r="H101" s="84" t="s">
-        <v>489</v>
+        <v>466</v>
       </c>
       <c r="I101" s="85" t="s">
-        <v>490</v>
+        <v>467</v>
       </c>
       <c r="J101" s="85" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="K101" s="85" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="L101" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="8:12">
       <c r="H102" s="84" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="I102" s="85" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
       <c r="J102" s="85" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="K102" s="85" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
       <c r="L102" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="8:12">
       <c r="H103" s="84" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="I103" s="85" t="s">
-        <v>497</v>
+        <v>474</v>
       </c>
       <c r="J103" s="85" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="K103" s="85" t="s">
-        <v>498</v>
+        <v>475</v>
       </c>
       <c r="L103" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="8:12">
       <c r="H104" s="84" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="I104" s="85" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="J104" s="85" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="K104" s="85" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="L104" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="8:12">
       <c r="H105" s="84" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="I105" s="85" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="J105" s="85" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="K105" s="85" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="L105" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="8:12">
       <c r="H106" s="84" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="I106" s="85" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="J106" s="85" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="K106" s="85" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="L106" s="84" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="8:12">
       <c r="H107" s="84" t="s">
-        <v>259</v>
+        <v>79</v>
       </c>
       <c r="I107" s="85" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="J107" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K107" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L107" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="8:12">
       <c r="H108" s="84" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="I108" s="85" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="J108" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K108" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L108" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="8:12">
       <c r="H109" s="84" t="s">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="I109" s="85" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="J109" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K109" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L109" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110" spans="8:12">
       <c r="H110" s="84" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="I110" s="85" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="J110" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K110" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L110" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" spans="8:12">
       <c r="H111" s="84" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="I111" s="85" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="J111" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K111" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L111" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="8:12">
       <c r="H112" s="84" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="I112" s="85" t="s">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="J112" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K112" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L112" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="8:12">
       <c r="H113" s="84" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="I113" s="85" t="s">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="J113" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K113" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L113" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="8:12">
       <c r="H114" s="84" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="I114" s="85" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="J114" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K114" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L114" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="8:12">
       <c r="H115" s="84" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="I115" s="85" t="s">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="J115" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K115" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L115" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116" spans="8:12">
       <c r="H116" s="84" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="I116" s="85" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="J116" s="85" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="K116" s="85" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
       <c r="L116" s="84" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
     </row>
     <row r="117" spans="8:12">
       <c r="H117" s="84" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="I117" s="85"/>
       <c r="J117" s="85"/>
@@ -40236,7 +40317,7 @@
     </row>
     <row r="118" spans="8:12">
       <c r="H118" s="84" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="I118" s="85"/>
       <c r="J118" s="85"/>
@@ -40245,7 +40326,7 @@
     </row>
     <row r="119" spans="8:12">
       <c r="H119" s="84" t="s">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="I119" s="85"/>
       <c r="J119" s="85"/>
@@ -40254,7 +40335,7 @@
     </row>
     <row r="120" spans="8:12">
       <c r="H120" s="84" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="I120" s="85"/>
       <c r="J120" s="85"/>
@@ -40263,7 +40344,7 @@
     </row>
     <row r="121" spans="8:12">
       <c r="H121" s="84" t="s">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="I121" s="85"/>
       <c r="J121" s="85"/>
@@ -40272,7 +40353,7 @@
     </row>
     <row r="122" spans="8:12">
       <c r="H122" s="84" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="I122" s="85"/>
       <c r="J122" s="85"/>
@@ -40281,7 +40362,7 @@
     </row>
     <row r="123" spans="8:12">
       <c r="H123" s="84" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="I123" s="85"/>
       <c r="J123" s="85"/>
@@ -40290,7 +40371,7 @@
     </row>
     <row r="124" spans="8:12">
       <c r="H124" s="84" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="I124" s="85"/>
       <c r="J124" s="85"/>
@@ -40299,7 +40380,7 @@
     </row>
     <row r="125" spans="8:12">
       <c r="H125" s="84" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="I125" s="85"/>
       <c r="J125" s="85"/>
@@ -40308,7 +40389,7 @@
     </row>
     <row r="126" spans="8:12">
       <c r="H126" s="84" t="s">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="I126" s="85"/>
       <c r="J126" s="85"/>
@@ -40317,7 +40398,7 @@
     </row>
     <row r="127" spans="8:12">
       <c r="H127" s="84" t="s">
-        <v>530</v>
+        <v>507</v>
       </c>
       <c r="I127" s="85"/>
       <c r="J127" s="85"/>
@@ -40326,7 +40407,7 @@
     </row>
     <row r="128" spans="8:12">
       <c r="H128" s="84" t="s">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="I128" s="85"/>
       <c r="J128" s="85"/>
@@ -40335,7 +40416,7 @@
     </row>
     <row r="129" spans="8:12">
       <c r="H129" s="84" t="s">
-        <v>532</v>
+        <v>509</v>
       </c>
       <c r="I129" s="85"/>
       <c r="J129" s="85"/>
@@ -40344,7 +40425,7 @@
     </row>
     <row r="130" spans="8:12">
       <c r="H130" s="84" t="s">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="I130" s="85"/>
       <c r="J130" s="85"/>
@@ -40353,7 +40434,7 @@
     </row>
     <row r="131" spans="8:12">
       <c r="H131" s="84" t="s">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="I131" s="85"/>
       <c r="J131" s="85"/>
@@ -40362,7 +40443,7 @@
     </row>
     <row r="132" spans="8:12">
       <c r="H132" s="84" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="I132" s="85"/>
       <c r="J132" s="85"/>
@@ -40371,7 +40452,7 @@
     </row>
     <row r="133" spans="8:12">
       <c r="H133" s="84" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="I133" s="85"/>
       <c r="J133" s="85"/>
@@ -40380,7 +40461,7 @@
     </row>
     <row r="134" spans="8:12">
       <c r="H134" s="84" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="I134" s="85"/>
       <c r="J134" s="85"/>
@@ -40389,7 +40470,7 @@
     </row>
     <row r="135" spans="8:12">
       <c r="H135" s="84" t="s">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="I135" s="85"/>
       <c r="J135" s="85"/>
@@ -40398,7 +40479,7 @@
     </row>
     <row r="136" spans="8:12">
       <c r="H136" s="84" t="s">
-        <v>539</v>
+        <v>516</v>
       </c>
       <c r="I136" s="85"/>
       <c r="J136" s="85"/>
@@ -40407,7 +40488,7 @@
     </row>
     <row r="137" spans="8:12">
       <c r="H137" s="84" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="I137" s="85"/>
       <c r="J137" s="85"/>
@@ -40416,7 +40497,7 @@
     </row>
     <row r="138" spans="8:12">
       <c r="H138" s="84" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="I138" s="85"/>
       <c r="J138" s="85"/>
@@ -40425,7 +40506,7 @@
     </row>
     <row r="139" spans="8:12">
       <c r="H139" s="84" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="I139" s="85"/>
       <c r="J139" s="85"/>
@@ -40434,7 +40515,7 @@
     </row>
     <row r="140" spans="8:12">
       <c r="H140" s="84" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="I140" s="85"/>
       <c r="J140" s="85"/>
@@ -40443,7 +40524,7 @@
     </row>
     <row r="141" spans="8:12">
       <c r="H141" s="84" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="I141" s="85"/>
       <c r="J141" s="85"/>
@@ -40452,7 +40533,7 @@
     </row>
     <row r="142" spans="8:12">
       <c r="H142" s="84" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="I142" s="85"/>
       <c r="J142" s="85"/>
@@ -40461,7 +40542,7 @@
     </row>
     <row r="143" spans="8:12">
       <c r="H143" s="84" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="I143" s="85"/>
       <c r="J143" s="85"/>
@@ -40470,7 +40551,7 @@
     </row>
     <row r="144" spans="8:12">
       <c r="H144" s="84" t="s">
-        <v>547</v>
+        <v>524</v>
       </c>
       <c r="I144" s="85"/>
       <c r="J144" s="85"/>
@@ -40479,7 +40560,7 @@
     </row>
     <row r="145" spans="8:12">
       <c r="H145" s="84" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="I145" s="85"/>
       <c r="J145" s="85"/>
@@ -40488,7 +40569,7 @@
     </row>
     <row r="146" spans="8:12">
       <c r="H146" s="84" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="I146" s="85"/>
       <c r="J146" s="85"/>
@@ -40497,7 +40578,7 @@
     </row>
     <row r="147" spans="8:12">
       <c r="H147" s="84" t="s">
-        <v>550</v>
+        <v>527</v>
       </c>
       <c r="I147" s="85"/>
       <c r="J147" s="85"/>
@@ -40506,7 +40587,7 @@
     </row>
     <row r="148" spans="8:12">
       <c r="H148" s="84" t="s">
-        <v>551</v>
+        <v>528</v>
       </c>
       <c r="I148" s="85"/>
       <c r="J148" s="85"/>
@@ -40515,7 +40596,7 @@
     </row>
     <row r="149" spans="8:12">
       <c r="H149" s="84" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="I149" s="85"/>
       <c r="J149" s="85"/>
@@ -40524,7 +40605,7 @@
     </row>
     <row r="150" spans="8:12">
       <c r="H150" s="84" t="s">
-        <v>553</v>
+        <v>530</v>
       </c>
       <c r="I150" s="85"/>
       <c r="J150" s="85"/>
@@ -40533,7 +40614,7 @@
     </row>
     <row r="151" spans="8:12">
       <c r="H151" s="84" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="I151" s="85"/>
       <c r="J151" s="85"/>
@@ -40542,7 +40623,7 @@
     </row>
     <row r="152" spans="8:12">
       <c r="H152" s="84" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="I152" s="85"/>
       <c r="J152" s="85"/>
@@ -40551,7 +40632,7 @@
     </row>
     <row r="153" spans="8:12">
       <c r="H153" s="84" t="s">
-        <v>556</v>
+        <v>533</v>
       </c>
       <c r="I153" s="85"/>
       <c r="J153" s="85"/>
@@ -40560,7 +40641,7 @@
     </row>
     <row r="154" spans="8:12">
       <c r="H154" s="84" t="s">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="I154" s="85"/>
       <c r="J154" s="85"/>
@@ -40569,7 +40650,7 @@
     </row>
     <row r="155" spans="8:12">
       <c r="H155" s="84" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="I155" s="85"/>
       <c r="J155" s="85"/>
@@ -40578,7 +40659,7 @@
     </row>
     <row r="156" spans="8:12">
       <c r="H156" s="84" t="s">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="I156" s="85"/>
       <c r="J156" s="85"/>
@@ -40587,7 +40668,7 @@
     </row>
     <row r="157" spans="8:12">
       <c r="H157" s="84" t="s">
-        <v>560</v>
+        <v>537</v>
       </c>
       <c r="I157" s="85"/>
       <c r="J157" s="85"/>
@@ -40596,7 +40677,7 @@
     </row>
     <row r="158" spans="8:12">
       <c r="H158" s="84" t="s">
-        <v>561</v>
+        <v>538</v>
       </c>
       <c r="I158" s="85"/>
       <c r="J158" s="85"/>
@@ -40605,7 +40686,7 @@
     </row>
     <row r="159" spans="8:12">
       <c r="H159" s="84" t="s">
-        <v>562</v>
+        <v>539</v>
       </c>
       <c r="I159" s="85"/>
       <c r="J159" s="85"/>
@@ -40614,7 +40695,7 @@
     </row>
     <row r="160" spans="8:12">
       <c r="H160" s="84" t="s">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="I160" s="85"/>
       <c r="J160" s="85"/>
@@ -40623,7 +40704,7 @@
     </row>
     <row r="161" spans="8:12">
       <c r="H161" s="84" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="I161" s="85"/>
       <c r="J161" s="85"/>
@@ -40632,7 +40713,7 @@
     </row>
     <row r="162" spans="8:12">
       <c r="H162" s="84" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="I162" s="85"/>
       <c r="J162" s="85"/>
@@ -40641,7 +40722,7 @@
     </row>
     <row r="163" spans="8:12">
       <c r="H163" s="84" t="s">
-        <v>566</v>
+        <v>543</v>
       </c>
       <c r="I163" s="85"/>
       <c r="J163" s="85"/>
@@ -40650,7 +40731,7 @@
     </row>
     <row r="164" spans="8:12">
       <c r="H164" s="84" t="s">
-        <v>567</v>
+        <v>544</v>
       </c>
       <c r="I164" s="85"/>
       <c r="J164" s="85"/>
@@ -40659,7 +40740,7 @@
     </row>
     <row r="165" spans="8:12">
       <c r="H165" s="84" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="I165" s="85"/>
       <c r="J165" s="85"/>
@@ -40668,7 +40749,7 @@
     </row>
     <row r="166" spans="8:12">
       <c r="H166" s="84" t="s">
-        <v>569</v>
+        <v>546</v>
       </c>
       <c r="I166" s="85"/>
       <c r="J166" s="85"/>
@@ -40677,7 +40758,7 @@
     </row>
     <row r="167" spans="8:12">
       <c r="H167" s="84" t="s">
-        <v>570</v>
+        <v>547</v>
       </c>
       <c r="I167" s="85"/>
       <c r="J167" s="85"/>
@@ -40686,7 +40767,7 @@
     </row>
     <row r="168" spans="8:12">
       <c r="H168" s="84" t="s">
-        <v>571</v>
+        <v>548</v>
       </c>
       <c r="I168" s="85"/>
       <c r="J168" s="85"/>
@@ -40695,7 +40776,7 @@
     </row>
     <row r="169" spans="8:12">
       <c r="H169" s="84" t="s">
-        <v>572</v>
+        <v>549</v>
       </c>
       <c r="I169" s="85"/>
       <c r="J169" s="85"/>
@@ -40704,7 +40785,7 @@
     </row>
     <row r="170" spans="8:12">
       <c r="H170" s="84" t="s">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="I170" s="85"/>
       <c r="J170" s="85"/>
@@ -40713,7 +40794,7 @@
     </row>
     <row r="171" spans="8:12">
       <c r="H171" s="84" t="s">
-        <v>574</v>
+        <v>551</v>
       </c>
       <c r="I171" s="85"/>
       <c r="J171" s="85"/>
@@ -40722,7 +40803,7 @@
     </row>
     <row r="172" spans="8:12">
       <c r="H172" s="84" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="I172" s="85"/>
       <c r="J172" s="85"/>
@@ -40731,7 +40812,7 @@
     </row>
     <row r="173" spans="8:12">
       <c r="H173" s="84" t="s">
-        <v>576</v>
+        <v>553</v>
       </c>
       <c r="I173" s="85"/>
       <c r="J173" s="85"/>
@@ -40740,7 +40821,7 @@
     </row>
     <row r="174" spans="8:12">
       <c r="H174" s="84" t="s">
-        <v>577</v>
+        <v>554</v>
       </c>
       <c r="I174" s="85"/>
       <c r="J174" s="85"/>
@@ -40749,7 +40830,7 @@
     </row>
     <row r="175" spans="8:12">
       <c r="H175" s="84" t="s">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="I175" s="85"/>
       <c r="J175" s="85"/>
@@ -40758,7 +40839,7 @@
     </row>
     <row r="176" spans="8:12">
       <c r="H176" s="84" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="I176" s="85"/>
       <c r="J176" s="85"/>
@@ -40767,7 +40848,7 @@
     </row>
     <row r="177" spans="8:12">
       <c r="H177" s="84" t="s">
-        <v>580</v>
+        <v>557</v>
       </c>
       <c r="I177" s="85"/>
       <c r="J177" s="85"/>
@@ -40776,7 +40857,7 @@
     </row>
     <row r="178" spans="8:12">
       <c r="H178" s="84" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="I178" s="85"/>
       <c r="J178" s="85"/>
@@ -40785,7 +40866,7 @@
     </row>
     <row r="179" spans="8:12">
       <c r="H179" s="84" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="I179" s="85"/>
       <c r="J179" s="85"/>
@@ -40794,7 +40875,7 @@
     </row>
     <row r="180" spans="8:12">
       <c r="H180" s="84" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="I180" s="85"/>
       <c r="J180" s="85"/>
@@ -40803,7 +40884,7 @@
     </row>
     <row r="181" spans="8:12">
       <c r="H181" s="84" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="I181" s="85"/>
       <c r="J181" s="85"/>
@@ -40812,7 +40893,7 @@
     </row>
     <row r="182" spans="8:12">
       <c r="H182" s="84" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="I182" s="85"/>
       <c r="J182" s="85"/>
@@ -40821,7 +40902,7 @@
     </row>
     <row r="183" spans="8:12">
       <c r="H183" s="84" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="I183" s="85"/>
       <c r="J183" s="85"/>
@@ -40830,7 +40911,7 @@
     </row>
     <row r="184" spans="8:12">
       <c r="H184" s="84" t="s">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="I184" s="85"/>
       <c r="J184" s="85"/>
@@ -40839,7 +40920,7 @@
     </row>
     <row r="185" spans="8:12">
       <c r="H185" s="84" t="s">
-        <v>588</v>
+        <v>565</v>
       </c>
       <c r="I185" s="85"/>
       <c r="J185" s="85"/>
@@ -40848,7 +40929,7 @@
     </row>
     <row r="186" spans="8:12">
       <c r="H186" s="84" t="s">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="I186" s="85"/>
       <c r="J186" s="85"/>
@@ -40857,7 +40938,7 @@
     </row>
     <row r="187" spans="8:12">
       <c r="H187" s="84" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="I187" s="85"/>
       <c r="J187" s="85"/>
@@ -40866,7 +40947,7 @@
     </row>
     <row r="188" spans="8:12">
       <c r="H188" s="84" t="s">
-        <v>591</v>
+        <v>568</v>
       </c>
       <c r="I188" s="85"/>
       <c r="J188" s="85"/>
@@ -40875,7 +40956,7 @@
     </row>
     <row r="189" spans="8:12">
       <c r="H189" s="84" t="s">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="I189" s="85"/>
       <c r="J189" s="85"/>
@@ -40884,7 +40965,7 @@
     </row>
     <row r="190" spans="8:12">
       <c r="H190" s="84" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="I190" s="85"/>
       <c r="J190" s="85"/>
@@ -40893,7 +40974,7 @@
     </row>
     <row r="191" spans="8:12">
       <c r="H191" s="84" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="I191" s="85"/>
       <c r="J191" s="85"/>
@@ -40902,7 +40983,7 @@
     </row>
     <row r="192" spans="8:12">
       <c r="H192" s="84" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="I192" s="85"/>
       <c r="J192" s="85"/>
@@ -40911,7 +40992,7 @@
     </row>
     <row r="193" spans="8:12">
       <c r="H193" s="84" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="I193" s="85"/>
       <c r="J193" s="85"/>
@@ -40920,7 +41001,7 @@
     </row>
     <row r="194" spans="8:12">
       <c r="H194" s="84" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="I194" s="85"/>
       <c r="J194" s="85"/>
@@ -40929,7 +41010,7 @@
     </row>
     <row r="195" spans="8:12">
       <c r="H195" s="84" t="s">
-        <v>598</v>
+        <v>575</v>
       </c>
       <c r="I195" s="85"/>
       <c r="J195" s="85"/>
@@ -40938,7 +41019,7 @@
     </row>
     <row r="196" spans="8:12">
       <c r="H196" s="84" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="I196" s="85"/>
       <c r="J196" s="85"/>
@@ -40947,7 +41028,7 @@
     </row>
     <row r="197" spans="8:12">
       <c r="H197" s="84" t="s">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c r="I197" s="85"/>
       <c r="J197" s="85"/>
@@ -40956,7 +41037,7 @@
     </row>
     <row r="198" spans="8:12">
       <c r="H198" s="84" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="I198" s="85"/>
       <c r="J198" s="85"/>
@@ -40965,7 +41046,7 @@
     </row>
     <row r="199" spans="8:12">
       <c r="H199" s="84" t="s">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="I199" s="85"/>
       <c r="J199" s="85"/>
@@ -40974,7 +41055,7 @@
     </row>
     <row r="200" spans="8:12">
       <c r="H200" s="84" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="I200" s="85"/>
       <c r="J200" s="85"/>
@@ -40983,7 +41064,7 @@
     </row>
     <row r="201" spans="8:12">
       <c r="H201" s="84" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="I201" s="85"/>
       <c r="J201" s="85"/>
@@ -40992,7 +41073,7 @@
     </row>
     <row r="202" spans="8:12">
       <c r="H202" s="84" t="s">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="I202" s="85"/>
       <c r="J202" s="85"/>
@@ -41001,7 +41082,7 @@
     </row>
     <row r="203" spans="8:12">
       <c r="H203" s="84" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="I203" s="85"/>
       <c r="J203" s="85"/>
@@ -41010,7 +41091,7 @@
     </row>
     <row r="204" spans="8:12">
       <c r="H204" s="84" t="s">
-        <v>607</v>
+        <v>584</v>
       </c>
       <c r="I204" s="85"/>
       <c r="J204" s="85"/>
@@ -41019,7 +41100,7 @@
     </row>
     <row r="205" spans="8:12">
       <c r="H205" s="84" t="s">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="I205" s="85"/>
       <c r="J205" s="85"/>
@@ -41028,7 +41109,7 @@
     </row>
     <row r="206" spans="8:12">
       <c r="H206" s="84" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="I206" s="85"/>
       <c r="J206" s="85"/>
@@ -41037,7 +41118,7 @@
     </row>
     <row r="207" spans="8:12">
       <c r="H207" s="84" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="I207" s="85"/>
       <c r="J207" s="85"/>
@@ -41046,7 +41127,7 @@
     </row>
     <row r="208" spans="8:12">
       <c r="H208" s="84" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="I208" s="85"/>
       <c r="J208" s="85"/>
@@ -41055,7 +41136,7 @@
     </row>
     <row r="209" spans="8:12">
       <c r="H209" s="84" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="I209" s="85"/>
       <c r="J209" s="85"/>
@@ -41064,7 +41145,7 @@
     </row>
     <row r="210" spans="8:12">
       <c r="H210" s="84" t="s">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="I210" s="85"/>
       <c r="J210" s="85"/>
@@ -41073,7 +41154,7 @@
     </row>
     <row r="211" spans="8:12">
       <c r="H211" s="84" t="s">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="I211" s="85"/>
       <c r="J211" s="85"/>
@@ -41082,7 +41163,7 @@
     </row>
     <row r="212" spans="8:12">
       <c r="H212" s="84" t="s">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="I212" s="85"/>
       <c r="J212" s="85"/>
@@ -41091,7 +41172,7 @@
     </row>
     <row r="213" spans="8:12">
       <c r="H213" s="84" t="s">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="I213" s="85"/>
       <c r="J213" s="85"/>
@@ -41100,7 +41181,7 @@
     </row>
     <row r="214" spans="8:12">
       <c r="H214" s="84" t="s">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="I214" s="85"/>
       <c r="J214" s="85"/>
@@ -41109,7 +41190,7 @@
     </row>
     <row r="215" spans="8:12">
       <c r="H215" s="84" t="s">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="I215" s="85"/>
       <c r="J215" s="85"/>
@@ -41118,7 +41199,7 @@
     </row>
     <row r="216" spans="8:12">
       <c r="H216" s="84" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="I216" s="85"/>
       <c r="J216" s="85"/>
@@ -41127,7 +41208,7 @@
     </row>
     <row r="217" spans="8:12">
       <c r="H217" s="84" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
       <c r="I217" s="85"/>
       <c r="J217" s="85"/>
@@ -41136,7 +41217,7 @@
     </row>
     <row r="218" spans="8:12">
       <c r="H218" s="84" t="s">
-        <v>621</v>
+        <v>598</v>
       </c>
       <c r="I218" s="85"/>
       <c r="J218" s="85"/>
@@ -41145,7 +41226,7 @@
     </row>
     <row r="219" spans="8:12">
       <c r="H219" s="84" t="s">
-        <v>622</v>
+        <v>599</v>
       </c>
       <c r="I219" s="85"/>
       <c r="J219" s="85"/>
@@ -41154,7 +41235,7 @@
     </row>
     <row r="220" spans="8:12">
       <c r="H220" s="84" t="s">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="I220" s="85"/>
       <c r="J220" s="85"/>
@@ -41163,7 +41244,7 @@
     </row>
     <row r="221" spans="8:12">
       <c r="H221" s="84" t="s">
-        <v>624</v>
+        <v>601</v>
       </c>
       <c r="I221" s="85"/>
       <c r="J221" s="85"/>
@@ -41172,7 +41253,7 @@
     </row>
     <row r="222" spans="8:12">
       <c r="H222" s="84" t="s">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="I222" s="85"/>
       <c r="J222" s="85"/>
@@ -41181,7 +41262,7 @@
     </row>
     <row r="223" spans="8:12">
       <c r="H223" s="84" t="s">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="I223" s="85"/>
       <c r="J223" s="85"/>
@@ -41190,7 +41271,7 @@
     </row>
     <row r="224" spans="8:12">
       <c r="H224" s="84" t="s">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="I224" s="85"/>
       <c r="J224" s="85"/>
@@ -41199,7 +41280,7 @@
     </row>
     <row r="225" spans="8:12">
       <c r="H225" s="84" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="I225" s="85"/>
       <c r="J225" s="85"/>
@@ -41208,7 +41289,7 @@
     </row>
     <row r="226" spans="8:12">
       <c r="H226" s="84" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="I226" s="85"/>
       <c r="J226" s="85"/>
@@ -41217,7 +41298,7 @@
     </row>
     <row r="227" spans="8:12">
       <c r="H227" s="84" t="s">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="I227" s="85"/>
       <c r="J227" s="85"/>
@@ -41226,7 +41307,7 @@
     </row>
     <row r="228" spans="8:12">
       <c r="H228" s="84" t="s">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="I228" s="85"/>
       <c r="J228" s="85"/>
@@ -41235,7 +41316,7 @@
     </row>
     <row r="229" spans="8:12">
       <c r="H229" s="84" t="s">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="I229" s="85"/>
       <c r="J229" s="85"/>
@@ -41244,7 +41325,7 @@
     </row>
     <row r="230" spans="8:12">
       <c r="H230" s="84" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="I230" s="85"/>
       <c r="J230" s="85"/>
@@ -41253,7 +41334,7 @@
     </row>
     <row r="231" spans="8:12">
       <c r="H231" s="84" t="s">
-        <v>634</v>
+        <v>611</v>
       </c>
       <c r="I231" s="85"/>
       <c r="J231" s="85"/>
@@ -41262,7 +41343,7 @@
     </row>
     <row r="232" spans="8:12">
       <c r="H232" s="84" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="I232" s="85"/>
       <c r="J232" s="85"/>
@@ -41271,7 +41352,7 @@
     </row>
     <row r="233" spans="8:12">
       <c r="H233" s="84" t="s">
-        <v>636</v>
+        <v>613</v>
       </c>
       <c r="I233" s="85"/>
       <c r="J233" s="85"/>
@@ -41280,7 +41361,7 @@
     </row>
     <row r="234" spans="8:12">
       <c r="H234" s="84" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="I234" s="85"/>
       <c r="J234" s="85"/>
@@ -41289,7 +41370,7 @@
     </row>
     <row r="235" spans="8:12">
       <c r="H235" s="84" t="s">
-        <v>638</v>
+        <v>615</v>
       </c>
       <c r="I235" s="85"/>
       <c r="J235" s="85"/>
@@ -41298,7 +41379,7 @@
     </row>
     <row r="236" spans="8:12">
       <c r="H236" s="84" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="I236" s="85"/>
       <c r="J236" s="85"/>
@@ -41307,7 +41388,7 @@
     </row>
     <row r="237" spans="8:12">
       <c r="H237" s="84" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
       <c r="I237" s="85"/>
       <c r="J237" s="85"/>
@@ -41316,7 +41397,7 @@
     </row>
     <row r="238" spans="8:12">
       <c r="H238" s="84" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="I238" s="85"/>
       <c r="J238" s="85"/>
@@ -41325,7 +41406,7 @@
     </row>
     <row r="239" spans="8:12">
       <c r="H239" s="84" t="s">
-        <v>642</v>
+        <v>619</v>
       </c>
       <c r="I239" s="85"/>
       <c r="J239" s="85"/>
@@ -41334,7 +41415,7 @@
     </row>
     <row r="240" spans="8:12">
       <c r="H240" s="84" t="s">
-        <v>643</v>
+        <v>620</v>
       </c>
       <c r="I240" s="85"/>
       <c r="J240" s="85"/>
@@ -41343,7 +41424,7 @@
     </row>
     <row r="241" spans="8:12">
       <c r="H241" s="84" t="s">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="I241" s="85"/>
       <c r="J241" s="85"/>
@@ -41352,7 +41433,7 @@
     </row>
     <row r="242" spans="8:12">
       <c r="H242" s="84" t="s">
-        <v>645</v>
+        <v>622</v>
       </c>
       <c r="I242" s="85"/>
       <c r="J242" s="85"/>
@@ -41361,7 +41442,7 @@
     </row>
     <row r="243" spans="8:12">
       <c r="H243" s="84" t="s">
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="I243" s="85"/>
       <c r="J243" s="85"/>
@@ -41370,7 +41451,7 @@
     </row>
     <row r="244" spans="8:12">
       <c r="H244" s="84" t="s">
-        <v>647</v>
+        <v>624</v>
       </c>
       <c r="I244" s="85"/>
       <c r="J244" s="85"/>
@@ -41379,7 +41460,7 @@
     </row>
     <row r="245" spans="8:12">
       <c r="H245" s="84" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="I245" s="85"/>
       <c r="J245" s="85"/>
@@ -41388,7 +41469,7 @@
     </row>
     <row r="246" spans="8:12">
       <c r="H246" s="84" t="s">
-        <v>649</v>
+        <v>626</v>
       </c>
       <c r="I246" s="85"/>
       <c r="J246" s="85"/>
@@ -41397,7 +41478,7 @@
     </row>
     <row r="247" spans="8:12">
       <c r="H247" s="84" t="s">
-        <v>650</v>
+        <v>627</v>
       </c>
       <c r="I247" s="85"/>
       <c r="J247" s="85"/>
@@ -41406,7 +41487,7 @@
     </row>
     <row r="248" spans="8:12">
       <c r="H248" s="84" t="s">
-        <v>651</v>
+        <v>628</v>
       </c>
       <c r="I248" s="85"/>
       <c r="J248" s="85"/>
@@ -41415,7 +41496,7 @@
     </row>
     <row r="249" spans="8:12">
       <c r="H249" s="84" t="s">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="I249" s="85"/>
       <c r="J249" s="85"/>
@@ -41424,7 +41505,7 @@
     </row>
     <row r="250" spans="8:12">
       <c r="H250" s="84" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="I250" s="85"/>
       <c r="J250" s="85"/>
@@ -41433,7 +41514,7 @@
     </row>
     <row r="251" spans="8:12">
       <c r="H251" s="84" t="s">
-        <v>654</v>
+        <v>631</v>
       </c>
       <c r="I251" s="85"/>
       <c r="J251" s="85"/>
@@ -41442,7 +41523,7 @@
     </row>
     <row r="252" spans="8:12">
       <c r="H252" s="84" t="s">
-        <v>655</v>
+        <v>632</v>
       </c>
       <c r="I252" s="85"/>
       <c r="J252" s="85"/>
@@ -41451,7 +41532,7 @@
     </row>
     <row r="253" spans="8:12">
       <c r="H253" s="84" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
       <c r="I253" s="85"/>
       <c r="J253" s="85"/>
@@ -41460,7 +41541,7 @@
     </row>
     <row r="254" spans="8:12">
       <c r="H254" s="84" t="s">
-        <v>657</v>
+        <v>634</v>
       </c>
       <c r="I254" s="85"/>
       <c r="J254" s="85"/>
@@ -41469,7 +41550,7 @@
     </row>
     <row r="255" spans="8:12">
       <c r="H255" s="84" t="s">
-        <v>658</v>
+        <v>635</v>
       </c>
       <c r="I255" s="85"/>
       <c r="J255" s="85"/>
@@ -41478,7 +41559,7 @@
     </row>
     <row r="256" spans="8:12">
       <c r="H256" s="84" t="s">
-        <v>659</v>
+        <v>636</v>
       </c>
       <c r="I256" s="85"/>
       <c r="J256" s="85"/>
@@ -41487,7 +41568,7 @@
     </row>
     <row r="257" spans="8:12">
       <c r="H257" s="84" t="s">
-        <v>660</v>
+        <v>637</v>
       </c>
       <c r="I257" s="85"/>
       <c r="J257" s="85"/>
@@ -41496,7 +41577,7 @@
     </row>
     <row r="258" spans="8:12">
       <c r="H258" s="84" t="s">
-        <v>661</v>
+        <v>638</v>
       </c>
       <c r="I258" s="85"/>
       <c r="J258" s="85"/>
@@ -41505,7 +41586,7 @@
     </row>
     <row r="259" spans="8:12">
       <c r="H259" s="84" t="s">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="I259" s="85"/>
       <c r="J259" s="85"/>
